--- a/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
@@ -226,6 +226,56 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lotus Infrastructure</author>
+  </authors>
+  <commentList>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>No revenue during build (Y0-Y2). Interest capitalizes into RAB. Equity deployed in phases.</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0" shapeId="0">
+      <text>
+        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="0" shapeId="0">
+      <text>
+        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="0" shapeId="0">
+      <text>
+        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0" shapeId="0">
+      <text>
+        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -517,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -583,6 +633,11 @@
           <t>Rate base (RAB) = total invested capital. Tariff set to provide return ON and OF capital. Very stable, predictable.</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Regulated Asset Base</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
@@ -593,6 +648,11 @@
       <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Y0-Y2 is construction with no revenue. Must fund construction, then refinance at COD (Commercial Operation Date).</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Years before COD</t>
         </is>
       </c>
     </row>
@@ -631,6 +691,10 @@
           <t>Construction interest added to RAB. You're earning on the interest you paid - improves economics.</t>
         </is>
       </c>
+      <c r="C12">
+        <f> Beg Bal × Rate</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
@@ -655,6 +719,11 @@
         </is>
       </c>
       <c r="B15" s="22" t="n"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Regulated Asset Base</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
@@ -667,6 +736,11 @@
           <t>Dev Y0 + Dev Y1 + Construction + Capitalized Interest. This is your 'invested capital' for rate-setting.</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Regulated Asset Base</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
@@ -679,6 +753,11 @@
           <t>RAB declines as you recover capital through depreciation. Exit RAB = COD RAB - Cumulative Depreciation.</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Regulated Asset Base</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
@@ -689,6 +768,11 @@
       <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Transmission trades at premium to RAB (1.15x) because of stability and growth. Exit EV = Exit RAB × 1.15x.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Regulated Asset Base</t>
         </is>
       </c>
     </row>
@@ -763,6 +847,10 @@
           <t>Single-asset, long-lived infrastructure. Higher covenant provides cushion for multi-decade asset life.</t>
         </is>
       </c>
+      <c r="C26">
+        <f> CFADS / Debt Service</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
@@ -824,8 +912,136 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
@@ -234,44 +234,9 @@
     <author>Lotus Infrastructure</author>
   </authors>
   <commentList>
-    <comment ref="C7" authorId="0" shapeId="0">
-      <text>
-        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
-      </text>
-    </comment>
-    <comment ref="C8" authorId="0" shapeId="0">
-      <text>
-        <t>No revenue during build (Y0-Y2). Interest capitalizes into RAB. Equity deployed in phases.</t>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
-      <text>
-        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
-      </text>
-    </comment>
-    <comment ref="C15" authorId="0" shapeId="0">
-      <text>
-        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
-      </text>
-    </comment>
-    <comment ref="C16" authorId="0" shapeId="0">
-      <text>
-        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
-      </text>
-    </comment>
-    <comment ref="C17" authorId="0" shapeId="0">
-      <text>
-        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
-      </text>
-    </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
-      <text>
-        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
-      </text>
-    </comment>
     <comment ref="C26" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
   </commentList>
@@ -633,11 +598,6 @@
           <t>Rate base (RAB) = total invested capital. Tariff set to provide return ON and OF capital. Very stable, predictable.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Regulated Asset Base</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
@@ -648,11 +608,6 @@
       <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Y0-Y2 is construction with no revenue. Must fund construction, then refinance at COD (Commercial Operation Date).</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Years before COD</t>
         </is>
       </c>
     </row>
@@ -691,10 +646,6 @@
           <t>Construction interest added to RAB. You're earning on the interest you paid - improves economics.</t>
         </is>
       </c>
-      <c r="C12">
-        <f> Beg Bal × Rate</f>
-        <v/>
-      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
@@ -719,11 +670,6 @@
         </is>
       </c>
       <c r="B15" s="22" t="n"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Regulated Asset Base</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
@@ -736,11 +682,6 @@
           <t>Dev Y0 + Dev Y1 + Construction + Capitalized Interest. This is your 'invested capital' for rate-setting.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Regulated Asset Base</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
@@ -753,11 +694,6 @@
           <t>RAB declines as you recover capital through depreciation. Exit RAB = COD RAB - Cumulative Depreciation.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Regulated Asset Base</t>
-        </is>
-      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
@@ -768,11 +704,6 @@
       <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Transmission trades at premium to RAB (1.15x) because of stability and growth. Exit EV = Exit RAB × 1.15x.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Regulated Asset Base</t>
         </is>
       </c>
     </row>
@@ -847,9 +778,10 @@
           <t>Single-asset, long-lived infrastructure. Higher covenant provides cushion for multi-decade asset life.</t>
         </is>
       </c>
-      <c r="C26">
-        <f> CFADS / Debt Service</f>
-        <v/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">

--- a/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuition Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +54,13 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000066CC"/>
     </font>
   </fonts>
   <fills count="7">
@@ -110,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -152,6 +161,8 @@
     <xf numFmtId="166" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -532,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -844,133 +855,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -978,6 +862,257 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: Transmission ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Time: 4 hours | Deliverables: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>SITUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>150-mile 345kV line, $180mm equity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1. What levered IRR at indicative price?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2. Downside DSCR under stress?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3. Key diligence items?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4. Protections to negotiate?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IC MEMO - COACHING FRAMEWORK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>1. EXECUTIVE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Tip: Lead with IRR and recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>2. TRANSACTION OVERVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>Tip: Sources &amp; uses, debt terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>3. INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>Tip: 3-4 bullets on attractiveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>4. KEY RISKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>Tip: Market, operational, regulatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>5. MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>Tip: Hedging, contracts, structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>6. SENSITIVITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>Tip: ±10-20% on key inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>7. RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>Tip: Clear yes/no with walk-away price</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1126,7 +1261,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="25">
-        <f>MIN(G85:N85)</f>
+        <f>IF(COUNTIF(G85:N85,"&gt;0")&gt;0,MINIFS(G85:N85,G85:N85,"&gt;0"),0)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
@@ -3507,6 +3507,7 @@
         <v/>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
@@ -3638,6 +3639,7 @@
         <v/>
       </c>
     </row>
+    <row r="106"/>
     <row r="107">
       <c r="A107" s="18" t="inlineStr">
         <is>
@@ -3711,7 +3713,7 @@
       </c>
       <c r="C111" s="6" t="inlineStr"/>
       <c r="D111" s="7">
-        <f>D109+D110+D104</f>
+        <f>D109+D110</f>
         <v/>
       </c>
     </row>
@@ -3724,10 +3726,11 @@
       <c r="B112" s="6" t="inlineStr"/>
       <c r="C112" s="6" t="inlineStr"/>
       <c r="D112" s="10">
-        <f>IF(ABS(D53+D104-D111)&lt;0.01,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
+        <f>IF(ABS(D105-D111)&lt;0.01,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113"/>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
@@ -3874,6 +3877,7 @@
         <v/>
       </c>
     </row>
+    <row r="121"/>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
@@ -3989,6 +3993,7 @@
         <v/>
       </c>
     </row>
+    <row r="126"/>
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuition Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -163,6 +163,12 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -237,21 +243,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Lotus Infrastructure</author>
-  </authors>
-  <commentList>
-    <comment ref="C26" authorId="0" shapeId="0">
-      <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -543,321 +534,652 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:A111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>TRANSMISSION MODEL - INTUITION GUIDE</t>
-        </is>
-      </c>
-      <c r="B1" s="19" t="inlineStr"/>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="18" t="inlineStr"/>
-      <c r="B2" s="19" t="inlineStr"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>SECTION</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>WHY IT MATTERS / KEY LOGIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="18" t="inlineStr"/>
-      <c r="B4" s="19" t="inlineStr"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>═══ BUSINESS CONTEXT ═══</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>What is Transmission?</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>High-voltage lines connecting generation to load centers. Regulated asset - earns FERC-approved ROE on rate base.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>RAB-Based Returns</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>Rate base (RAB) = total invested capital. Tariff set to provide return ON and OF capital. Very stable, predictable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>Construction Period</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>Y0-Y2 is construction with no revenue. Must fund construction, then refinance at COD (Commercial Operation Date).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="19" t="inlineStr"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>═══ CONSTRUCTION FINANCING ═══</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>Construction Loan (85%)</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>Short-term loan to fund construction. Higher leverage acceptable because it's temporary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>Interest Capitalization</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>Construction interest added to RAB. You're earning on the interest you paid - improves economics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>Phased Equity</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>Equity deployed over multiple years as construction progresses. IRR calculation must account for timing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="18" t="inlineStr"/>
-      <c r="B14" s="19" t="inlineStr"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>═══ RAB CALCULATION ═══</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>RAB at COD</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>Dev Y0 + Dev Y1 + Construction + Capitalized Interest. This is your 'invested capital' for rate-setting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>RAB Depreciation</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>RAB declines as you recover capital through depreciation. Exit RAB = COD RAB - Cumulative Depreciation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>Exit at xRAB Multiple</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>Transmission trades at premium to RAB (1.15x) because of stability and growth. Exit EV = Exit RAB × 1.15x.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="18" t="inlineStr"/>
-      <c r="B19" s="19" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>═══ REFINANCING AT COD ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>What Happens at COD</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>Construction loan + capitalized interest repaid. Replaced with term debt (60% of RAB) + refinancing equity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Refi Equity Calculation</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>(Construction Loan + Capitalized Interest) - Term Debt = equity needed to bridge the gap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="18" t="inlineStr"/>
-      <c r="B23" s="19" t="inlineStr"/>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>═══ DEBT STRUCTURE ═══</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Why Sculpted?</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>Regulated tariff provides very predictable cash flows. Sculpting is efficient - size debt service to DSCR target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>Higher DSCR (1.40x)</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>Single-asset, long-lived infrastructure. Higher covenant provides cushion for multi-decade asset life.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>No Debt Y1-Y2</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>Construction period - no revenue to service debt. Term debt starts at COD (Y3).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="18" t="inlineStr"/>
-      <c r="B28" s="19" t="inlineStr"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>═══ COMMON IC QUESTIONS ═══</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>Q: What's the regulatory risk?</t>
-        </is>
-      </c>
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>FERC could reduce allowed ROE. Mitigant: historically stable, bipartisan support for transmission investment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
-        <is>
-          <t>Q: Why does transmission trade at premium?</t>
-        </is>
-      </c>
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>Stable regulated returns, long asset life (40+ years), critical infrastructure status. Scarcity value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
-        <is>
-          <t>Q: What if construction is delayed?</t>
-        </is>
-      </c>
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>Higher capitalized interest, later revenue start. Run sensitivity on COD delay showing IRR impact.</t>
+    <row r="1">
+      <c r="A1">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>LOTUS INFRASTRUCTURE PARTNERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: ELECTRIC TRANSMISSION LINE ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TIME: 4 Hours | DATE: January 2026 | DELIVERABLES: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>--- MODEL TIMELINE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Year 0 (2025): Development costs; construction loan drawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Year 1 (2026): Major construction; AFUDC accrues</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Year 2 (2027): Construction completion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Year 3 (2028): COD - Term debt takeout; tariff revenue starts</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Year 10 (2035): Model horizon (asset life 40+ years)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>--- SITUATION ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Lotus Infrastructure Partners is evaluating equity investment in a
+150-mile, 345 kV transmission line under development in SPP. FERC has
+approved 10.5% ROE with 50/50 regulatory capital structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>Development began in 2025 (Y0), with construction in 2026-2027 and COD
+expected in Year 3 (2028). Total project cost is ~$585mm including
+development, construction, and AFUDC during construction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>Upon COD, revenue comes from FERC-approved tariff based on rate base and
+allowed ROE. The line has 40+ years expected useful life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>Lotus is offered $180mm equity during construction. Commitment needed by
+March 15, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>--- KEY VALUE DRIVERS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>* FERC ROE: Allowed return on equity sets revenue requirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>* Rate Base: Capital invested that earns the allowed return</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>* Construction Timing: Delays reduce returns; AFUDC accrues during build</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>* Regulatory Risk: ROE can change in FERC rate case proceedings</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>--- STEP-BY-STEP MODEL BUILDING GUIDE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>STEP-BY-STEP MODEL BUILDING GUIDE FOR TRANSMISSION</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>KEY DIFFERENCES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>- CONSTRUCTION PERIOD before operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>- AFUDC (capitalized interest) accrues to rate base</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>- Revenue is REGULATED formula, not market prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>- Two financing events: Construction loan -&gt; Term debt takeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="32" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="32" t="inlineStr">
+        <is>
+          <t>1. CONSTRUCTION PERIOD (Years 0-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Development Costs: $35mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Construction Costs: $550mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Construction Loan: 85% of construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   AFUDC = Const Loan x Interest x Avg Period = ~$35mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   AFUDC accrues to Rate Base (non-cash during construction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="32" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>2. RATE BASE AT COD (Year 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Rate Base = Development + Construction + AFUDC</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   = $35mm + $550mm + ~$35mm = ~$620mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="32" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>3. TERM DEBT TAKEOUT AT COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   At COD, Construction Loan repaid by Term Debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Term Debt = Rate Base x Regulatory Debt % = $620mm x 50% = $310mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Use RATE BASE (not construction cost) for debt sizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="32" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>4. REVENUE CALCULATION (Years 3+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Revenue = Rate Base x (ROE + Depreciation/Life + O&amp;M/RB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="32" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>5. S&amp;U - TWO EVENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   At Close (Y0): Development costs, fees -&gt; Const loan, equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   At COD (Y3): Const loan payoff -&gt; Term debt, permanent equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   DSRA is a USE (funded by debt/equity), NOT a Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="32" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="32" t="inlineStr">
+        <is>
+          <t>6. SCULPTED DEBT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Regulated cash flows support sculpted debt at 1.40x DSCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>--- HOW TO AVOID CIRCULARITY ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TRANSMISSION - SPECIAL CONSIDERATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>No sweep mechanics - sculpted debt only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AFUDC creates complexity but not circularity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>S&amp;U RULES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>- DSRA is a Use, NOT a Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>- Balance check compares Total Uses vs Total Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>- Construction loan payoff must be included at COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>--- ALTERNATIVE SCENARIOS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A. Acquisition at COD (No Construction):</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Skip construction period</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Buy operating asset at Rate Base multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B. Rate Case During Hold:</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - ROE may change in rate proceedings</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Model +/- 50bp ROE sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>C. Rate Base Growth:</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Capital additions over time</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Growing rate base = growing earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="29" t="inlineStr">
+        <is>
+          <t>--- QA CHECKS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>QA CHECKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1. AFUDC included in Rate Base at COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2. S&amp;U balances at BOTH close and COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>3. DSRA is only a Use, never a Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>4. Revenue ties to rate base x allowed returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>5. ROE sensitivity shows material impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="29" t="inlineStr">
+        <is>
+          <t>--- HINTS &amp; PITFALLS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="30" t="inlineStr">
+        <is>
+          <t>* AFUDC is often $20-40mm - don't forget to capitalize it</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="30" t="inlineStr">
+        <is>
+          <t>* 50bp ROE change at 10x rate base = 5% equity value impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="30" t="inlineStr">
+        <is>
+          <t>* Construction delays kill returns - model delay scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="30" t="inlineStr">
+        <is>
+          <t>* DSRA is a Use funded by debt/equity, NOT a source</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="29" t="inlineStr">
+        <is>
+          <t>--- INTERVIEW QUESTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Q: Walk me through AFUDC and how it affects rate base at COD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Q: How does a 50bp ROE change affect your equity returns?</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Q: What construction risks would you prioritize in diligence?</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Q: How would you structure the construction loan takeout?</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1143,38 +1465,60 @@
           <t>Transmission Model - Lotus Infrastructure Partners</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N1" s="2" t="n">
-        <v>10</v>
+      <c r="D1" s="31" t="inlineStr">
+        <is>
+          <t>Y0 (2025)</t>
+        </is>
+      </c>
+      <c r="E1" s="31" t="inlineStr">
+        <is>
+          <t>Y1 (2026)</t>
+        </is>
+      </c>
+      <c r="F1" s="31" t="inlineStr">
+        <is>
+          <t>Y2 (2027)</t>
+        </is>
+      </c>
+      <c r="G1" s="31" t="inlineStr">
+        <is>
+          <t>Y3 (2028)</t>
+        </is>
+      </c>
+      <c r="H1" s="31" t="inlineStr">
+        <is>
+          <t>Y4 (2029)</t>
+        </is>
+      </c>
+      <c r="I1" s="31" t="inlineStr">
+        <is>
+          <t>Y5 (2030)</t>
+        </is>
+      </c>
+      <c r="J1" s="31" t="inlineStr">
+        <is>
+          <t>Y6 (2031)</t>
+        </is>
+      </c>
+      <c r="K1" s="31" t="inlineStr">
+        <is>
+          <t>Y7 (2032)</t>
+        </is>
+      </c>
+      <c r="L1" s="31" t="inlineStr">
+        <is>
+          <t>Y8 (2033)</t>
+        </is>
+      </c>
+      <c r="M1" s="31" t="inlineStr">
+        <is>
+          <t>Y9 (2034)</t>
+        </is>
+      </c>
+      <c r="N1" s="31" t="inlineStr">
+        <is>
+          <t>Y10 (2035)</t>
+        </is>
       </c>
     </row>
     <row r="2">
@@ -3507,7 +3851,6 @@
         <v/>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
@@ -3639,7 +3982,6 @@
         <v/>
       </c>
     </row>
-    <row r="106"/>
     <row r="107">
       <c r="A107" s="18" t="inlineStr">
         <is>
@@ -3730,7 +4072,6 @@
         <v/>
       </c>
     </row>
-    <row r="113"/>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
@@ -3877,7 +4218,6 @@
         <v/>
       </c>
     </row>
-    <row r="121"/>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
@@ -3993,7 +4333,6 @@
         <v/>
       </c>
     </row>
-    <row r="126"/>
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,6 +86,12 @@
       <color rgb="001F4E79"/>
       <sz val="12"/>
     </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -143,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,6 +210,14 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3179,196 +3193,196 @@
     <row r="5">
       <c r="A5" s="33" t="inlineStr">
         <is>
-          <t>═══════════════════ CONTROL PANEL ═══════════════════</t>
-        </is>
-      </c>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="44" t="n"/>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="n"/>
+      <c r="B6" s="44" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>Contract Years</t>
-        </is>
-      </c>
+          <t>Revenue Mode</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>If Hybrid: years of contracted revenue</t>
+          <t>Merchant / Contracted / Hybrid</t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Merchant</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0 = N/A; else last year of PTC/ITC</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="46" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
           <t>Debt Sweep</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Sweep %</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Only active if Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="44" t="n"/>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="47" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Avg CFADS (Y3-Y10)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="7">
-        <f>AVERAGE(G76:N76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y3-Y10)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="25">
-        <f>IF(COUNTIF(G85:N85,"&gt;0")&gt;0,MINIFS(G85:N85,G85:N85,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="26">
-        <f>D124</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="25">
-        <f>D125</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="26">
-        <f>D129</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>═══ QA CHECKS ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -3381,9 +3395,9 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S&amp;U Balance</t>
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
@@ -6276,196 +6290,196 @@
     <row r="5">
       <c r="A5" s="33" t="inlineStr">
         <is>
-          <t>═══════════════════ CONTROL PANEL ═══════════════════</t>
-        </is>
-      </c>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="44" t="n"/>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="n"/>
+      <c r="B6" s="44" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>Contract Years</t>
-        </is>
-      </c>
+          <t>Revenue Mode</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>If Hybrid: years of contracted revenue</t>
+          <t>Merchant / Contracted / Hybrid</t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Merchant</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0 = N/A; else last year of PTC/ITC</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="46" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
           <t>Debt Sweep</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Sweep %</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Only active if Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="44" t="n"/>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="47" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Avg CFADS (Y3-Y10)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="7">
-        <f>AVERAGE(G76:N76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y3-Y10)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="25">
-        <f>IF(COUNTIF(G85:N85,"&gt;0")&gt;0,MINIFS(G85:N85,G85:N85,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="26">
-        <f>D124</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="25">
-        <f>D125</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="26">
-        <f>D129</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>═══ QA CHECKS ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -6478,9 +6492,9 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S&amp;U Balance</t>
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>

--- a/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +92,11 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -149,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,6 +223,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3055,7 +3061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N139"/>
+  <dimension ref="A1:N140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3137,46 +3143,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="50" t="inlineStr">
+        <is>
+          <t>═══ DRILL MODE: Key formulas blanked. Rebuild using Formula Logic hints in Column C. ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>═══ AUDIT STRIP ═══</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>RAB at COD</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="7">
-        <f>$D$53</f>
-        <v/>
-      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Y3 EBITDA (First Op Year)</t>
+          <t>RAB at COD</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3186,297 +3182,290 @@
       </c>
       <c r="C4" s="6" t="inlineStr"/>
       <c r="D4" s="7">
-        <f>G70</f>
+        <f>$D$53</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Y3 EBITDA (First Op Year)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>═══════════ CONTROL PANEL ═══════════</t>
         </is>
       </c>
-      <c r="B5" s="44" t="n"/>
-      <c r="C5" s="44" t="n"/>
-      <c r="D5" s="44" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="44" t="n"/>
       <c r="B6" s="44" t="n"/>
       <c r="C6" s="44" t="n"/>
       <c r="D6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
+      <c r="A7" s="44" t="n"/>
       <c r="B7" s="44" t="n"/>
       <c r="C7" s="44" t="n"/>
       <c r="D7" s="44" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="B8" s="44" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D8" s="42" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
-          <t>Contract End Year</t>
+          <t>Revenue Mode</t>
         </is>
       </c>
       <c r="B9" s="44" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
+          <t>Merchant / Contracted / Hybrid</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>0 = pure merchant; else year PPA ends</t>
         </is>
       </c>
-      <c r="D9" s="42" t="n">
+      <c r="D10" s="42" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="44" t="n"/>
-      <c r="B10" s="44" t="n"/>
-      <c r="C10" s="44" t="n"/>
-      <c r="D10" s="44" t="n"/>
-    </row>
     <row r="11">
-      <c r="A11" s="45" t="inlineStr">
-        <is>
-          <t>TIMING</t>
-        </is>
-      </c>
+      <c r="A11" s="44" t="n"/>
       <c r="B11" s="44" t="n"/>
       <c r="C11" s="44" t="n"/>
       <c r="D11" s="44" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>Exit Year</t>
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>TIMING</t>
         </is>
       </c>
       <c r="B12" s="44" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>5 / 7 / 10</t>
-        </is>
-      </c>
-      <c r="D12" s="42" t="n">
-        <v>7</v>
-      </c>
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="44" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>Tax Credit End Year</t>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B13" s="44" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
           <t>0 = N/A; else last year of PTC/ITC</t>
         </is>
       </c>
-      <c r="D13" s="42" t="n">
+      <c r="D14" s="42" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="44" t="n"/>
-      <c r="B14" s="44" t="n"/>
-      <c r="C14" s="44" t="n"/>
-      <c r="D14" s="44" t="n"/>
-    </row>
     <row r="15">
-      <c r="A15" s="45" t="inlineStr">
-        <is>
-          <t>DEBT</t>
-        </is>
-      </c>
+      <c r="A15" s="44" t="n"/>
       <c r="B15" s="44" t="n"/>
       <c r="C15" s="44" t="n"/>
-      <c r="D15" s="46" t="n"/>
+      <c r="D15" s="44" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
-        <is>
-          <t>Debt Sweep</t>
+      <c r="A16" s="45" t="inlineStr">
+        <is>
+          <t>DEBT</t>
         </is>
       </c>
       <c r="B16" s="44" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF (for sweep assets)</t>
-        </is>
-      </c>
-      <c r="D16" s="28" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="46" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Sweep %</t>
+          <t>Debt Sweep</t>
         </is>
       </c>
       <c r="B17" s="44" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Sweep %</t>
+        </is>
+      </c>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
           <t>Active when Sweep = ON</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="44" t="n"/>
-      <c r="B18" s="44" t="n"/>
-      <c r="C18" s="44" t="n"/>
-      <c r="D18" s="47" t="n"/>
-    </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
+      <c r="A19" s="44" t="n"/>
       <c r="B19" s="44" t="n"/>
       <c r="C19" s="44" t="n"/>
-      <c r="D19" s="48" t="n"/>
+      <c r="D19" s="47" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="49" t="inlineStr">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="48" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="B20" s="44" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="B21" s="44" t="n"/>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D20" s="42" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="33" t="inlineStr">
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr"/>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="10">
-        <f>D112</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Debt Payoff Y10</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
       <c r="D22" s="10">
-        <f>IF(N84&lt;1,"PASS","FAIL")</f>
+        <f>D112</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Min DSCR ≥ 1.35x</t>
+          <t>Debt Payoff Y10</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
       <c r="D23" s="10">
-        <f>IF(D6&gt;=1.35,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+        <f>IF(N84&lt;1,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Min DSCR ≥ 1.35x</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr"/>
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>CONSTRUCTION INPUTS</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Development Cost Y0</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Pre-construction dev</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>15</v>
-      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Development Cost Y1</t>
+          <t>Development Cost Y0</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -3486,17 +3475,17 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Continued development</t>
+          <t>Pre-construction dev</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Construction Cost Y2</t>
+          <t>Development Cost Y1</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -3506,277 +3495,281 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Main construction</t>
+          <t>Continued development</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>550</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>Construction Cost Y2</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Main construction</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>COD Year</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Commercial operation date</t>
         </is>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D31" s="12" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>ASSET INPUTS</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Transfer Capacity</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Line rating</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>3200</v>
-      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Transfer Capacity</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Expected uptime</t>
-        </is>
-      </c>
-      <c r="D34" s="27" t="n">
-        <v>0.98</v>
+          <t>Line rating</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>3200</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Expected uptime</t>
+        </is>
+      </c>
+      <c r="D35" s="27" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>Asset Life</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>For depreciation</t>
         </is>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D36" s="12" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>PRICING INPUTS</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
-      <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Tariff Rate</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>$/kW-yr</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>FERC-approved</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="n">
-        <v>32</v>
-      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
+          <t>Tariff Rate</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>$/kW-yr</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>FERC-approved</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
           <t>Tariff Escalation</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>%/yr</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Rate increase</t>
         </is>
       </c>
-      <c r="D39" s="27" t="n">
+      <c r="D40" s="27" t="n">
         <v>0.02</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>COST INPUTS</t>
         </is>
       </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" s="4" t="n"/>
-      <c r="L41" s="4" t="n"/>
-      <c r="M41" s="4" t="n"/>
-      <c r="N41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>O&amp;M Y3</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Post-COD O&amp;M</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>O&amp;M Y3</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Post-COD O&amp;M</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
           <t>O&amp;M Escalation</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>%/yr</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>Cost escalation</t>
         </is>
       </c>
-      <c r="D43" s="27" t="n">
+      <c r="D44" s="27" t="n">
         <v>0.025</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>FINANCING INPUTS</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
-      <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Construction Debt %</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Const loan leverage</t>
-        </is>
-      </c>
-      <c r="D46" s="27" t="n">
-        <v>0.85</v>
-      </c>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Term Debt % of RAB</t>
+          <t>Construction Debt %</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -3786,17 +3779,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Refi at COD</t>
+          <t>Const loan leverage</t>
         </is>
       </c>
       <c r="D47" s="27" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Term Debt % of RAB</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -3806,218 +3799,220 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>All-in rate</t>
+          <t>Refi at COD</t>
         </is>
       </c>
       <c r="D48" s="27" t="n">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>DSRA Months</t>
+          <t>Interest Rate</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Debt service reserve</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="n">
-        <v>6</v>
+          <t>All-in rate</t>
+        </is>
+      </c>
+      <c r="D49" s="27" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Target DSCR</t>
+          <t>DSRA Months</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>For sculpting</t>
-        </is>
-      </c>
-      <c r="D50" s="28" t="n">
-        <v>1.4</v>
+          <t>Debt service reserve</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
+          <t>Target DSCR</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>For sculpting</t>
+        </is>
+      </c>
+      <c r="D51" s="28" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
           <t>Lock-up DSCR</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Distribution threshold</t>
         </is>
       </c>
-      <c r="D51" s="28" t="n">
+      <c r="D52" s="28" t="n">
         <v>1.15</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>EXIT INPUTS</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="n"/>
-      <c r="L53" s="4" t="n"/>
-      <c r="M53" s="4" t="n"/>
-      <c r="N53" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Exit xRAB Multiple</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Exit at RAB multiple</t>
-        </is>
-      </c>
-      <c r="D54" s="28" t="n">
-        <v>1.15</v>
-      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
+      <c r="N54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
+          <t>Exit xRAB Multiple</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Exit at RAB multiple</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
           <t>Exit Year</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>Hold period</t>
         </is>
       </c>
-      <c r="D55" s="12" t="n">
+      <c r="D56" s="12" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>TAX INPUTS</t>
         </is>
       </c>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="n"/>
-      <c r="J57" s="4" t="n"/>
-      <c r="K57" s="4" t="n"/>
-      <c r="L57" s="4" t="n"/>
-      <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>Tax Rate</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>Blended federal + state</t>
         </is>
       </c>
-      <c r="D58" s="27" t="n">
+      <c r="D59" s="27" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>CALCULATED ITEMS</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="4" t="n"/>
-      <c r="G60" s="4" t="n"/>
-      <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="n"/>
-      <c r="J60" s="4" t="n"/>
-      <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n"/>
-      <c r="M60" s="4" t="n"/>
-      <c r="N60" s="4" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Construction Loan</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Const Cost × Const Debt %</t>
-        </is>
-      </c>
-      <c r="D61" s="15">
-        <f>$D$19*$D$36</f>
-        <v/>
-      </c>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="n"/>
+      <c r="M61" s="4" t="n"/>
+      <c r="N61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Construction Interest</t>
+          <t>Construction Loan</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -4027,18 +4022,18 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Capitalized into RAB</t>
+          <t>Const Cost × Const Debt %</t>
         </is>
       </c>
       <c r="D62" s="15">
-        <f>$D$51*$D$38</f>
+        <f>$D$19*$D$36</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>RAB at COD</t>
+          <t>Construction Interest</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -4048,18 +4043,15 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Dev + Const + Int</t>
-        </is>
-      </c>
-      <c r="D63" s="15">
-        <f>$D$17+$D$18+$D$19+$D$52</f>
-        <v/>
-      </c>
+          <t>Capitalized into RAB</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Term Debt</t>
+          <t>RAB at COD</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -4069,76 +4061,81 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>RAB × Term Debt %</t>
+          <t>Dev + Const + Int</t>
         </is>
       </c>
       <c r="D64" s="15">
-        <f>$D$53*$D$37</f>
+        <f>$D$17+$D$18+$D$19+$D$52</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
+          <t>Term Debt</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>RAB × Term Debt %</t>
+        </is>
+      </c>
+      <c r="D65" s="15">
+        <f>$D$53*$D$37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
           <t>Annual Depreciation</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>RAB / Asset Life</t>
         </is>
       </c>
-      <c r="D65" s="15">
+      <c r="D66" s="15">
         <f>$D$53/$D$25</f>
         <v/>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>CONSTRUCTION PHASE (Y0-Y2)</t>
         </is>
       </c>
-      <c r="B67" s="4" t="n"/>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n"/>
-      <c r="F67" s="4" t="n"/>
-      <c r="G67" s="4" t="n"/>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="n"/>
-      <c r="J67" s="4" t="n"/>
-      <c r="K67" s="4" t="n"/>
-      <c r="L67" s="4" t="n"/>
-      <c r="M67" s="4" t="n"/>
-      <c r="N67" s="4" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Development Equity Y0</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr"/>
-      <c r="D68" s="16">
-        <f>$D$17</f>
-        <v/>
-      </c>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
+      <c r="I68" s="4" t="n"/>
+      <c r="J68" s="4" t="n"/>
+      <c r="K68" s="4" t="n"/>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="4" t="n"/>
+      <c r="N68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Development Equity Y1</t>
+          <t>Development Equity Y0</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -4147,15 +4144,15 @@
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr"/>
-      <c r="E69" s="16">
-        <f>$D$18</f>
+      <c r="D69" s="16">
+        <f>$D$17</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Construction Equity Y2</t>
+          <t>Development Equity Y1</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -4163,20 +4160,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>Const × (1-Debt%)</t>
-        </is>
-      </c>
-      <c r="F70" s="16">
-        <f>$D$19*(1-$D$36)</f>
+      <c r="C70" s="6" t="inlineStr"/>
+      <c r="E70" s="16">
+        <f>$D$18</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Refinancing Equity Y3</t>
+          <t>Construction Equity Y2</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -4186,356 +4179,264 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Const Loan - Term Debt</t>
-        </is>
-      </c>
-      <c r="G71" s="16">
-        <f>($D$51+$D$52)-$D$54</f>
+          <t>Const × (1-Debt%)</t>
+        </is>
+      </c>
+      <c r="F71" s="16">
+        <f>$D$19*(1-$D$36)</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
+          <t>Refinancing Equity Y3</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Const Loan - Term Debt</t>
+        </is>
+      </c>
+      <c r="G72" s="16">
+        <f>($D$51+$D$52)-$D$54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
           <t>Total Equity Invested</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr"/>
-      <c r="D72" s="7">
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr"/>
+      <c r="D73" s="7">
         <f>D58+E59+F60+G61</f>
         <v/>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>OPERATING MODEL (Y3+ Post-COD)</t>
         </is>
       </c>
-      <c r="B74" s="4" t="n"/>
-      <c r="C74" s="4" t="n"/>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n"/>
-      <c r="F74" s="4" t="n"/>
-      <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="n"/>
-      <c r="J74" s="4" t="n"/>
-      <c r="K74" s="4" t="n"/>
-      <c r="L74" s="4" t="n"/>
-      <c r="M74" s="4" t="n"/>
-      <c r="N74" s="4" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>Tariff Rate</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>$/kW-yr</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>Escalated</t>
         </is>
       </c>
-      <c r="E75" s="15">
+      <c r="E76" s="15">
         <f>0</f>
         <v/>
       </c>
-      <c r="F75" s="15">
+      <c r="F76" s="15">
         <f>0</f>
         <v/>
       </c>
-      <c r="G75" s="15">
+      <c r="G76" s="15">
         <f>$D$28*(1+$D$29)^(3-3)</f>
         <v/>
       </c>
-      <c r="H75" s="15">
+      <c r="H76" s="15">
         <f>$D$28*(1+$D$29)^(4-3)</f>
         <v/>
       </c>
-      <c r="I75" s="15">
+      <c r="I76" s="15">
         <f>$D$28*(1+$D$29)^(5-3)</f>
         <v/>
       </c>
-      <c r="J75" s="15">
+      <c r="J76" s="15">
         <f>$D$28*(1+$D$29)^(6-3)</f>
         <v/>
       </c>
-      <c r="K75" s="15">
+      <c r="K76" s="15">
         <f>$D$28*(1+$D$29)^(7-3)</f>
         <v/>
       </c>
-      <c r="L75" s="15">
+      <c r="L76" s="15">
         <f>$D$28*(1+$D$29)^(8-3)</f>
         <v/>
       </c>
-      <c r="M75" s="15">
+      <c r="M76" s="15">
         <f>$D$28*(1+$D$29)^(9-3)</f>
         <v/>
       </c>
-      <c r="N75" s="15">
+      <c r="N76" s="15">
         <f>$D$28*(1+$D$29)^(10-3)</f>
         <v/>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>Cap × Tariff × Avail × 1000/1M</t>
-        </is>
-      </c>
-      <c r="E77" s="15">
-        <f>$D$23*E65*$D$24*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="F77" s="15">
-        <f>$D$23*F65*$D$24*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="G77" s="15">
-        <f>$D$23*G65*$D$24*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="H77" s="15">
-        <f>$D$23*H65*$D$24*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="I77" s="15">
-        <f>$D$23*I65*$D$24*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="J77" s="15">
-        <f>$D$23*J65*$D$24*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="K77" s="15">
-        <f>$D$23*K65*$D$24*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="L77" s="15">
-        <f>$D$23*L65*$D$24*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="M77" s="15">
-        <f>$D$23*M65*$D$24*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="N77" s="15">
-        <f>$D$23*N65*$D$24*1000/1000000</f>
-        <v/>
-      </c>
-    </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Cap × Tariff × Avail × 1000/1M</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr"/>
+      <c r="F78" s="15" t="inlineStr"/>
+      <c r="G78" s="15" t="inlineStr"/>
+      <c r="H78" s="15" t="inlineStr"/>
+      <c r="I78" s="15" t="inlineStr"/>
+      <c r="J78" s="15" t="inlineStr"/>
+      <c r="K78" s="15" t="inlineStr"/>
+      <c r="L78" s="15" t="inlineStr"/>
+      <c r="M78" s="15" t="inlineStr"/>
+      <c r="N78" s="15" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
           <t>O&amp;M Cost</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>Post-COD only</t>
         </is>
       </c>
-      <c r="E78" s="15">
+      <c r="E79" s="15">
         <f>0</f>
         <v/>
       </c>
-      <c r="F78" s="15">
+      <c r="F79" s="15">
         <f>0</f>
         <v/>
       </c>
-      <c r="G78" s="15">
+      <c r="G79" s="15">
         <f>$D$32*(1+$D$33)^(3-3)</f>
         <v/>
       </c>
-      <c r="H78" s="15">
+      <c r="H79" s="15">
         <f>$D$32*(1+$D$33)^(4-3)</f>
         <v/>
       </c>
-      <c r="I78" s="15">
+      <c r="I79" s="15">
         <f>$D$32*(1+$D$33)^(5-3)</f>
         <v/>
       </c>
-      <c r="J78" s="15">
+      <c r="J79" s="15">
         <f>$D$32*(1+$D$33)^(6-3)</f>
         <v/>
       </c>
-      <c r="K78" s="15">
+      <c r="K79" s="15">
         <f>$D$32*(1+$D$33)^(7-3)</f>
         <v/>
       </c>
-      <c r="L78" s="15">
+      <c r="L79" s="15">
         <f>$D$32*(1+$D$33)^(8-3)</f>
         <v/>
       </c>
-      <c r="M78" s="15">
+      <c r="M79" s="15">
         <f>$D$32*(1+$D$33)^(9-3)</f>
         <v/>
       </c>
-      <c r="N78" s="15">
+      <c r="N79" s="15">
         <f>$D$32*(1+$D$33)^(10-3)</f>
         <v/>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr"/>
-      <c r="E80" s="7">
-        <f>E67-E68</f>
-        <v/>
-      </c>
-      <c r="F80" s="7">
-        <f>F67-F68</f>
-        <v/>
-      </c>
-      <c r="G80" s="7">
-        <f>G67-G68</f>
-        <v/>
-      </c>
-      <c r="H80" s="7">
-        <f>H67-H68</f>
-        <v/>
-      </c>
-      <c r="I80" s="7">
-        <f>I67-I68</f>
-        <v/>
-      </c>
-      <c r="J80" s="7">
-        <f>J67-J68</f>
-        <v/>
-      </c>
-      <c r="K80" s="7">
-        <f>K67-K68</f>
-        <v/>
-      </c>
-      <c r="L80" s="7">
-        <f>L67-L68</f>
-        <v/>
-      </c>
-      <c r="M80" s="7">
-        <f>M67-M68</f>
-        <v/>
-      </c>
-      <c r="N80" s="7">
-        <f>N67-N68</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr"/>
+      <c r="E81" s="7" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr"/>
+      <c r="K81" s="7" t="inlineStr"/>
+      <c r="L81" s="7" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+      <c r="N81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>CASH FLOW</t>
         </is>
       </c>
-      <c r="B82" s="4" t="n"/>
-      <c r="C82" s="4" t="n"/>
-      <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="n"/>
-      <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
-      <c r="N82" s="4" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>Post-COD only</t>
-        </is>
-      </c>
-      <c r="E83" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F83" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="H83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="I83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="J83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="K83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="L83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="M83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="N83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
+      <c r="B83" s="4" t="n"/>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="n"/>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n"/>
+      <c r="G83" s="4" t="n"/>
+      <c r="H83" s="4" t="n"/>
+      <c r="I83" s="4" t="n"/>
+      <c r="J83" s="4" t="n"/>
+      <c r="K83" s="4" t="n"/>
+      <c r="L83" s="4" t="n"/>
+      <c r="M83" s="4" t="n"/>
+      <c r="N83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -4545,54 +4446,54 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>EBITDA - Depreciation</t>
+          <t>Post-COD only</t>
         </is>
       </c>
       <c r="E84" s="15">
-        <f>E70-E73</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="F84" s="15">
-        <f>F70-F73</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="G84" s="15">
-        <f>G70-G73</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="H84" s="15">
-        <f>H70-H73</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="I84" s="15">
-        <f>I70-I73</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="J84" s="15">
-        <f>J70-J73</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="K84" s="15">
-        <f>K70-K73</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="L84" s="15">
-        <f>L70-L73</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="M84" s="15">
-        <f>M70-M73</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="N84" s="15">
-        <f>N70-N73</f>
+        <f>$D$55</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>EBIT</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -4602,184 +4503,99 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, EBIT) × Tax Rate</t>
-        </is>
-      </c>
-      <c r="E85" s="15">
-        <f>MAX(0,E74)*$D$48</f>
-        <v/>
-      </c>
-      <c r="F85" s="15">
-        <f>MAX(0,F74)*$D$48</f>
-        <v/>
-      </c>
-      <c r="G85" s="15">
-        <f>MAX(0,G74)*$D$48</f>
-        <v/>
-      </c>
-      <c r="H85" s="15">
-        <f>MAX(0,H74)*$D$48</f>
-        <v/>
-      </c>
-      <c r="I85" s="15">
-        <f>MAX(0,I74)*$D$48</f>
-        <v/>
-      </c>
-      <c r="J85" s="15">
-        <f>MAX(0,J74)*$D$48</f>
-        <v/>
-      </c>
-      <c r="K85" s="15">
-        <f>MAX(0,K74)*$D$48</f>
-        <v/>
-      </c>
-      <c r="L85" s="15">
-        <f>MAX(0,L74)*$D$48</f>
-        <v/>
-      </c>
-      <c r="M85" s="15">
-        <f>MAX(0,M74)*$D$48</f>
-        <v/>
-      </c>
-      <c r="N85" s="15">
-        <f>MAX(0,N74)*$D$48</f>
-        <v/>
-      </c>
+          <t>EBITDA - Depreciation</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr"/>
+      <c r="F85" s="15" t="inlineStr"/>
+      <c r="G85" s="15" t="inlineStr"/>
+      <c r="H85" s="15" t="inlineStr"/>
+      <c r="I85" s="15" t="inlineStr"/>
+      <c r="J85" s="15" t="inlineStr"/>
+      <c r="K85" s="15" t="inlineStr"/>
+      <c r="L85" s="15" t="inlineStr"/>
+      <c r="M85" s="15" t="inlineStr"/>
+      <c r="N85" s="15" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>MAX(0, EBIT) × Tax Rate</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr"/>
+      <c r="F86" s="15" t="inlineStr"/>
+      <c r="G86" s="15" t="inlineStr"/>
+      <c r="H86" s="15" t="inlineStr"/>
+      <c r="I86" s="15" t="inlineStr"/>
+      <c r="J86" s="15" t="inlineStr"/>
+      <c r="K86" s="15" t="inlineStr"/>
+      <c r="L86" s="15" t="inlineStr"/>
+      <c r="M86" s="15" t="inlineStr"/>
+      <c r="N86" s="15" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
           <t>CFADS</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>EBITDA - Taxes</t>
         </is>
       </c>
-      <c r="E86" s="7">
-        <f>E70-E75</f>
-        <v/>
-      </c>
-      <c r="F86" s="7">
-        <f>F70-F75</f>
-        <v/>
-      </c>
-      <c r="G86" s="7">
-        <f>G70-G75</f>
-        <v/>
-      </c>
-      <c r="H86" s="7">
-        <f>H70-H75</f>
-        <v/>
-      </c>
-      <c r="I86" s="7">
-        <f>I70-I75</f>
-        <v/>
-      </c>
-      <c r="J86" s="7">
-        <f>J70-J75</f>
-        <v/>
-      </c>
-      <c r="K86" s="7">
-        <f>K70-K75</f>
-        <v/>
-      </c>
-      <c r="L86" s="7">
-        <f>L70-L75</f>
-        <v/>
-      </c>
-      <c r="M86" s="7">
-        <f>M70-M75</f>
-        <v/>
-      </c>
-      <c r="N86" s="7">
-        <f>N70-N75</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr"/>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr"/>
+      <c r="J87" s="7" t="inlineStr"/>
+      <c r="K87" s="7" t="inlineStr"/>
+      <c r="L87" s="7" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+      <c r="N87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>DEBT SCHEDULE (Sculpted 1.40x, Y3+ Only)</t>
         </is>
       </c>
-      <c r="B88" s="4" t="n"/>
-      <c r="C88" s="4" t="n"/>
-      <c r="D88" s="4" t="n"/>
-      <c r="E88" s="4" t="n"/>
-      <c r="F88" s="4" t="n"/>
-      <c r="G88" s="4" t="n"/>
-      <c r="H88" s="4" t="n"/>
-      <c r="I88" s="4" t="n"/>
-      <c r="J88" s="4" t="n"/>
-      <c r="K88" s="4" t="n"/>
-      <c r="L88" s="4" t="n"/>
-      <c r="M88" s="4" t="n"/>
-      <c r="N88" s="4" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>Beginning Balance</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr"/>
-      <c r="E89" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F89" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G89" s="15">
-        <f>$D$54</f>
-        <v/>
-      </c>
-      <c r="H89" s="15">
-        <f>G84</f>
-        <v/>
-      </c>
-      <c r="I89" s="15">
-        <f>H84</f>
-        <v/>
-      </c>
-      <c r="J89" s="15">
-        <f>I84</f>
-        <v/>
-      </c>
-      <c r="K89" s="15">
-        <f>J84</f>
-        <v/>
-      </c>
-      <c r="L89" s="15">
-        <f>K84</f>
-        <v/>
-      </c>
-      <c r="M89" s="15">
-        <f>L84</f>
-        <v/>
-      </c>
-      <c r="N89" s="15">
-        <f>M84</f>
-        <v/>
-      </c>
+      <c r="B89" s="4" t="n"/>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="4" t="n"/>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
+      <c r="G89" s="4" t="n"/>
+      <c r="H89" s="4" t="n"/>
+      <c r="I89" s="4" t="n"/>
+      <c r="J89" s="4" t="n"/>
+      <c r="K89" s="4" t="n"/>
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="4" t="n"/>
+      <c r="N89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Beginning Balance</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -4787,56 +4603,52 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>Beg Bal × Int Rate</t>
-        </is>
-      </c>
+      <c r="C90" s="6" t="inlineStr"/>
       <c r="E90" s="15">
-        <f>E79*$D$38</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="F90" s="15">
-        <f>F79*$D$38</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="G90" s="15">
-        <f>G79*$D$38</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="H90" s="15">
-        <f>H79*$D$38</f>
+        <f>G84</f>
         <v/>
       </c>
       <c r="I90" s="15">
-        <f>I79*$D$38</f>
+        <f>H84</f>
         <v/>
       </c>
       <c r="J90" s="15">
-        <f>J79*$D$38</f>
+        <f>I84</f>
         <v/>
       </c>
       <c r="K90" s="15">
-        <f>K79*$D$38</f>
+        <f>J84</f>
         <v/>
       </c>
       <c r="L90" s="15">
-        <f>L79*$D$38</f>
+        <f>K84</f>
         <v/>
       </c>
       <c r="M90" s="15">
-        <f>M79*$D$38</f>
+        <f>L84</f>
         <v/>
       </c>
       <c r="N90" s="15">
-        <f>N79*$D$38</f>
+        <f>M84</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Target Debt Service</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -4846,54 +4658,24 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>CFADS / Target DSCR</t>
-        </is>
-      </c>
-      <c r="E91" s="15">
-        <f>IF(E76&gt;0,E76/$D$40,0)</f>
-        <v/>
-      </c>
-      <c r="F91" s="15">
-        <f>IF(F76&gt;0,F76/$D$40,0)</f>
-        <v/>
-      </c>
-      <c r="G91" s="15">
-        <f>IF(G76&gt;0,G76/$D$40,0)</f>
-        <v/>
-      </c>
-      <c r="H91" s="15">
-        <f>IF(H76&gt;0,H76/$D$40,0)</f>
-        <v/>
-      </c>
-      <c r="I91" s="15">
-        <f>IF(I76&gt;0,I76/$D$40,0)</f>
-        <v/>
-      </c>
-      <c r="J91" s="15">
-        <f>IF(J76&gt;0,J76/$D$40,0)</f>
-        <v/>
-      </c>
-      <c r="K91" s="15">
-        <f>IF(K76&gt;0,K76/$D$40,0)</f>
-        <v/>
-      </c>
-      <c r="L91" s="15">
-        <f>IF(L76&gt;0,L76/$D$40,0)</f>
-        <v/>
-      </c>
-      <c r="M91" s="15">
-        <f>IF(M76&gt;0,M76/$D$40,0)</f>
-        <v/>
-      </c>
-      <c r="N91" s="15">
-        <f>IF(N76&gt;0,N76/$D$40,0)</f>
-        <v/>
-      </c>
+          <t>Beg Bal × Int Rate</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr"/>
+      <c r="F91" s="15" t="inlineStr"/>
+      <c r="G91" s="15" t="inlineStr"/>
+      <c r="H91" s="15" t="inlineStr"/>
+      <c r="I91" s="15" t="inlineStr"/>
+      <c r="J91" s="15" t="inlineStr"/>
+      <c r="K91" s="15" t="inlineStr"/>
+      <c r="L91" s="15" t="inlineStr"/>
+      <c r="M91" s="15" t="inlineStr"/>
+      <c r="N91" s="15" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Sculpted Principal</t>
+          <t>Target Debt Service</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -4903,54 +4685,24 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>Target DS - Interest</t>
-        </is>
-      </c>
-      <c r="E92" s="15">
-        <f>MIN(MAX(0,E81-E80),E79)</f>
-        <v/>
-      </c>
-      <c r="F92" s="15">
-        <f>MIN(MAX(0,F81-F80),F79)</f>
-        <v/>
-      </c>
-      <c r="G92" s="15">
-        <f>MIN(MAX(0,G81-G80),G79)</f>
-        <v/>
-      </c>
-      <c r="H92" s="15">
-        <f>MIN(MAX(0,H81-H80),H79)</f>
-        <v/>
-      </c>
-      <c r="I92" s="15">
-        <f>MIN(MAX(0,I81-I80),I79)</f>
-        <v/>
-      </c>
-      <c r="J92" s="15">
-        <f>MIN(MAX(0,J81-J80),J79)</f>
-        <v/>
-      </c>
-      <c r="K92" s="15">
-        <f>MIN(MAX(0,K81-K80),K79)</f>
-        <v/>
-      </c>
-      <c r="L92" s="15">
-        <f>MIN(MAX(0,L81-L80),L79)</f>
-        <v/>
-      </c>
-      <c r="M92" s="15">
-        <f>MIN(MAX(0,M81-M80),M79)</f>
-        <v/>
-      </c>
-      <c r="N92" s="15">
-        <f>MIN(MAX(0,N81-N80),N79)</f>
-        <v/>
-      </c>
+          <t>CFADS / Target DSCR</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr"/>
+      <c r="F92" s="15" t="inlineStr"/>
+      <c r="G92" s="15" t="inlineStr"/>
+      <c r="H92" s="15" t="inlineStr"/>
+      <c r="I92" s="15" t="inlineStr"/>
+      <c r="J92" s="15" t="inlineStr"/>
+      <c r="K92" s="15" t="inlineStr"/>
+      <c r="L92" s="15" t="inlineStr"/>
+      <c r="M92" s="15" t="inlineStr"/>
+      <c r="N92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Actual Debt Service</t>
+          <t>Sculpted Principal</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -4960,54 +4712,24 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Interest + Principal</t>
-        </is>
-      </c>
-      <c r="E93" s="15">
-        <f>E80+E82</f>
-        <v/>
-      </c>
-      <c r="F93" s="15">
-        <f>F80+F82</f>
-        <v/>
-      </c>
-      <c r="G93" s="15">
-        <f>G80+G82</f>
-        <v/>
-      </c>
-      <c r="H93" s="15">
-        <f>H80+H82</f>
-        <v/>
-      </c>
-      <c r="I93" s="15">
-        <f>I80+I82</f>
-        <v/>
-      </c>
-      <c r="J93" s="15">
-        <f>J80+J82</f>
-        <v/>
-      </c>
-      <c r="K93" s="15">
-        <f>K80+K82</f>
-        <v/>
-      </c>
-      <c r="L93" s="15">
-        <f>L80+L82</f>
-        <v/>
-      </c>
-      <c r="M93" s="15">
-        <f>M80+M82</f>
-        <v/>
-      </c>
-      <c r="N93" s="15">
-        <f>N80+N82</f>
-        <v/>
-      </c>
+          <t>Target DS - Interest</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr"/>
+      <c r="F93" s="15" t="inlineStr"/>
+      <c r="G93" s="15" t="inlineStr"/>
+      <c r="H93" s="15" t="inlineStr"/>
+      <c r="I93" s="15" t="inlineStr"/>
+      <c r="J93" s="15" t="inlineStr"/>
+      <c r="K93" s="15" t="inlineStr"/>
+      <c r="L93" s="15" t="inlineStr"/>
+      <c r="M93" s="15" t="inlineStr"/>
+      <c r="N93" s="15" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Ending Balance</t>
+          <t>Actual Debt Service</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -5017,192 +4739,129 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>Beg - Principal</t>
+          <t>Interest + Principal</t>
         </is>
       </c>
       <c r="E94" s="15">
-        <f>MAX(0,E79-E82)</f>
+        <f>E80+E82</f>
         <v/>
       </c>
       <c r="F94" s="15">
-        <f>MAX(0,F79-F82)</f>
+        <f>F80+F82</f>
         <v/>
       </c>
       <c r="G94" s="15">
-        <f>MAX(0,G79-G82)</f>
+        <f>G80+G82</f>
         <v/>
       </c>
       <c r="H94" s="15">
-        <f>MAX(0,H79-H82)</f>
+        <f>H80+H82</f>
         <v/>
       </c>
       <c r="I94" s="15">
-        <f>MAX(0,I79-I82)</f>
+        <f>I80+I82</f>
         <v/>
       </c>
       <c r="J94" s="15">
-        <f>MAX(0,J79-J82)</f>
+        <f>J80+J82</f>
         <v/>
       </c>
       <c r="K94" s="15">
-        <f>MAX(0,K79-K82)</f>
+        <f>K80+K82</f>
         <v/>
       </c>
       <c r="L94" s="15">
-        <f>MAX(0,L79-L82)</f>
+        <f>L80+L82</f>
         <v/>
       </c>
       <c r="M94" s="15">
-        <f>MAX(0,M79-M82)</f>
+        <f>M80+M82</f>
         <v/>
       </c>
       <c r="N94" s="15">
-        <f>MAX(0,N79-N82)</f>
+        <f>N80+N82</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
+          <t>Ending Balance</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Beg - Principal</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr"/>
+      <c r="F95" s="15" t="inlineStr"/>
+      <c r="G95" s="15" t="inlineStr"/>
+      <c r="H95" s="15" t="inlineStr"/>
+      <c r="I95" s="15" t="inlineStr"/>
+      <c r="J95" s="15" t="inlineStr"/>
+      <c r="K95" s="15" t="inlineStr"/>
+      <c r="L95" s="15" t="inlineStr"/>
+      <c r="M95" s="15" t="inlineStr"/>
+      <c r="N95" s="15" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
           <t>Actual DSCR</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
         <is>
           <t>CFADS / Actual DS</t>
         </is>
       </c>
-      <c r="E95" s="25">
-        <f>IF(E83&gt;0,E76/E83,0)</f>
-        <v/>
-      </c>
-      <c r="F95" s="25">
-        <f>IF(F83&gt;0,F76/F83,0)</f>
-        <v/>
-      </c>
-      <c r="G95" s="25">
-        <f>IF(G83&gt;0,G76/G83,0)</f>
-        <v/>
-      </c>
-      <c r="H95" s="25">
-        <f>IF(H83&gt;0,H76/H83,0)</f>
-        <v/>
-      </c>
-      <c r="I95" s="25">
-        <f>IF(I83&gt;0,I76/I83,0)</f>
-        <v/>
-      </c>
-      <c r="J95" s="25">
-        <f>IF(J83&gt;0,J76/J83,0)</f>
-        <v/>
-      </c>
-      <c r="K95" s="25">
-        <f>IF(K83&gt;0,K76/K83,0)</f>
-        <v/>
-      </c>
-      <c r="L95" s="25">
-        <f>IF(L83&gt;0,L76/L83,0)</f>
-        <v/>
-      </c>
-      <c r="M95" s="25">
-        <f>IF(M83&gt;0,M76/M83,0)</f>
-        <v/>
-      </c>
-      <c r="N95" s="25">
-        <f>IF(N83&gt;0,N76/N83,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="E96" s="25" t="inlineStr"/>
+      <c r="F96" s="25" t="inlineStr"/>
+      <c r="G96" s="25" t="inlineStr"/>
+      <c r="H96" s="25" t="inlineStr"/>
+      <c r="I96" s="25" t="inlineStr"/>
+      <c r="J96" s="25" t="inlineStr"/>
+      <c r="K96" s="25" t="inlineStr"/>
+      <c r="L96" s="25" t="inlineStr"/>
+      <c r="M96" s="25" t="inlineStr"/>
+      <c r="N96" s="25" t="inlineStr"/>
+    </row>
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>DSRA (Debt Service Reserve Account)</t>
         </is>
       </c>
-      <c r="B97" s="4" t="n"/>
-      <c r="C97" s="4" t="n"/>
-      <c r="D97" s="4" t="n"/>
-      <c r="E97" s="4" t="n"/>
-      <c r="F97" s="4" t="n"/>
-      <c r="G97" s="4" t="n"/>
-      <c r="H97" s="4" t="n"/>
-      <c r="I97" s="4" t="n"/>
-      <c r="J97" s="4" t="n"/>
-      <c r="K97" s="4" t="n"/>
-      <c r="L97" s="4" t="n"/>
-      <c r="M97" s="4" t="n"/>
-      <c r="N97" s="4" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>DSRA Target</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>Next Yr DS × DSRA Months / 12</t>
-        </is>
-      </c>
-      <c r="D98" s="15">
-        <f>G83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="E98" s="15">
-        <f>G83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="F98" s="15">
-        <f>G83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="G98" s="15">
-        <f>H83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="H98" s="15">
-        <f>I83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="I98" s="15">
-        <f>J83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="J98" s="15">
-        <f>K83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="K98" s="15">
-        <f>L83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="L98" s="15">
-        <f>M83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="M98" s="15">
-        <f>N83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="N98" s="15">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="B98" s="4" t="n"/>
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="n"/>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="n"/>
+      <c r="G98" s="4" t="n"/>
+      <c r="H98" s="4" t="n"/>
+      <c r="I98" s="4" t="n"/>
+      <c r="J98" s="4" t="n"/>
+      <c r="K98" s="4" t="n"/>
+      <c r="L98" s="4" t="n"/>
+      <c r="M98" s="4" t="n"/>
+      <c r="N98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>DSRA Beginning</t>
+          <t>DSRA Target</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -5210,56 +4869,60 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr"/>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Next Yr DS × DSRA Months / 12</t>
+        </is>
+      </c>
       <c r="D99" s="15">
+        <f>G83*$D$39/12</f>
+        <v/>
+      </c>
+      <c r="E99" s="15">
+        <f>G83*$D$39/12</f>
+        <v/>
+      </c>
+      <c r="F99" s="15">
+        <f>G83*$D$39/12</f>
+        <v/>
+      </c>
+      <c r="G99" s="15">
+        <f>H83*$D$39/12</f>
+        <v/>
+      </c>
+      <c r="H99" s="15">
+        <f>I83*$D$39/12</f>
+        <v/>
+      </c>
+      <c r="I99" s="15">
+        <f>J83*$D$39/12</f>
+        <v/>
+      </c>
+      <c r="J99" s="15">
+        <f>K83*$D$39/12</f>
+        <v/>
+      </c>
+      <c r="K99" s="15">
+        <f>L83*$D$39/12</f>
+        <v/>
+      </c>
+      <c r="L99" s="15">
+        <f>M83*$D$39/12</f>
+        <v/>
+      </c>
+      <c r="M99" s="15">
+        <f>N83*$D$39/12</f>
+        <v/>
+      </c>
+      <c r="N99" s="15">
         <f>0</f>
-        <v/>
-      </c>
-      <c r="E99" s="15">
-        <f>D91</f>
-        <v/>
-      </c>
-      <c r="F99" s="15">
-        <f>E91</f>
-        <v/>
-      </c>
-      <c r="G99" s="15">
-        <f>F91</f>
-        <v/>
-      </c>
-      <c r="H99" s="15">
-        <f>G91</f>
-        <v/>
-      </c>
-      <c r="I99" s="15">
-        <f>H91</f>
-        <v/>
-      </c>
-      <c r="J99" s="15">
-        <f>I91</f>
-        <v/>
-      </c>
-      <c r="K99" s="15">
-        <f>J91</f>
-        <v/>
-      </c>
-      <c r="L99" s="15">
-        <f>K91</f>
-        <v/>
-      </c>
-      <c r="M99" s="15">
-        <f>L91</f>
-        <v/>
-      </c>
-      <c r="N99" s="15">
-        <f>M91</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>DSRA Funding/(Release)</t>
+          <t>DSRA Beginning</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -5267,354 +4930,366 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>Target - Beginning</t>
-        </is>
-      </c>
+      <c r="C100" s="6" t="inlineStr"/>
       <c r="D100" s="15">
-        <f>D88-D89</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E100" s="15">
-        <f>E88-E89</f>
+        <f>D91</f>
         <v/>
       </c>
       <c r="F100" s="15">
-        <f>F88-F89</f>
+        <f>E91</f>
         <v/>
       </c>
       <c r="G100" s="15">
-        <f>G88-G89</f>
+        <f>F91</f>
         <v/>
       </c>
       <c r="H100" s="15">
-        <f>H88-H89</f>
+        <f>G91</f>
         <v/>
       </c>
       <c r="I100" s="15">
-        <f>I88-I89</f>
+        <f>H91</f>
         <v/>
       </c>
       <c r="J100" s="15">
-        <f>J88-J89</f>
+        <f>I91</f>
         <v/>
       </c>
       <c r="K100" s="15">
-        <f>K88-K89</f>
+        <f>J91</f>
         <v/>
       </c>
       <c r="L100" s="15">
-        <f>L88-L89</f>
+        <f>K91</f>
         <v/>
       </c>
       <c r="M100" s="15">
-        <f>M88-M89</f>
+        <f>L91</f>
         <v/>
       </c>
       <c r="N100" s="15">
-        <f>N88-N89</f>
+        <f>M91</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
+          <t>DSRA Funding/(Release)</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Target - Beginning</t>
+        </is>
+      </c>
+      <c r="D101" s="15">
+        <f>D88-D89</f>
+        <v/>
+      </c>
+      <c r="E101" s="15">
+        <f>E88-E89</f>
+        <v/>
+      </c>
+      <c r="F101" s="15">
+        <f>F88-F89</f>
+        <v/>
+      </c>
+      <c r="G101" s="15">
+        <f>G88-G89</f>
+        <v/>
+      </c>
+      <c r="H101" s="15">
+        <f>H88-H89</f>
+        <v/>
+      </c>
+      <c r="I101" s="15">
+        <f>I88-I89</f>
+        <v/>
+      </c>
+      <c r="J101" s="15">
+        <f>J88-J89</f>
+        <v/>
+      </c>
+      <c r="K101" s="15">
+        <f>K88-K89</f>
+        <v/>
+      </c>
+      <c r="L101" s="15">
+        <f>L88-L89</f>
+        <v/>
+      </c>
+      <c r="M101" s="15">
+        <f>M88-M89</f>
+        <v/>
+      </c>
+      <c r="N101" s="15">
+        <f>N88-N89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
           <t>DSRA Ending</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t>Beginning + Funding</t>
         </is>
       </c>
-      <c r="D101" s="15">
+      <c r="D102" s="15">
         <f>D89+D90</f>
         <v/>
       </c>
-      <c r="E101" s="15">
+      <c r="E102" s="15">
         <f>E89+E90</f>
         <v/>
       </c>
-      <c r="F101" s="15">
+      <c r="F102" s="15">
         <f>F89+F90</f>
         <v/>
       </c>
-      <c r="G101" s="15">
+      <c r="G102" s="15">
         <f>G89+G90</f>
         <v/>
       </c>
-      <c r="H101" s="15">
+      <c r="H102" s="15">
         <f>H89+H90</f>
         <v/>
       </c>
-      <c r="I101" s="15">
+      <c r="I102" s="15">
         <f>I89+I90</f>
         <v/>
       </c>
-      <c r="J101" s="15">
+      <c r="J102" s="15">
         <f>J89+J90</f>
         <v/>
       </c>
-      <c r="K101" s="15">
+      <c r="K102" s="15">
         <f>K89+K90</f>
         <v/>
       </c>
-      <c r="L101" s="15">
+      <c r="L102" s="15">
         <f>L89+L90</f>
         <v/>
       </c>
-      <c r="M101" s="15">
+      <c r="M102" s="15">
         <f>M89+M90</f>
         <v/>
       </c>
-      <c r="N101" s="15">
+      <c r="N102" s="15">
         <f>N89+N90</f>
         <v/>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>DISTRIBUTION WATERFALL</t>
         </is>
       </c>
-      <c r="B103" s="4" t="n"/>
-      <c r="C103" s="4" t="n"/>
-      <c r="D103" s="4" t="n"/>
-      <c r="E103" s="4" t="n"/>
-      <c r="F103" s="4" t="n"/>
-      <c r="G103" s="4" t="n"/>
-      <c r="H103" s="4" t="n"/>
-      <c r="I103" s="4" t="n"/>
-      <c r="J103" s="4" t="n"/>
-      <c r="K103" s="4" t="n"/>
-      <c r="L103" s="4" t="n"/>
-      <c r="M103" s="4" t="n"/>
-      <c r="N103" s="4" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>Cash Available for Distribution</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>CFADS - DS - DSRA Fund</t>
-        </is>
-      </c>
-      <c r="E104" s="15">
-        <f>E76-E83-E90</f>
-        <v/>
-      </c>
-      <c r="F104" s="15">
-        <f>F76-F83-F90</f>
-        <v/>
-      </c>
-      <c r="G104" s="15">
-        <f>G76-G83-G90</f>
-        <v/>
-      </c>
-      <c r="H104" s="15">
-        <f>H76-H83-H90</f>
-        <v/>
-      </c>
-      <c r="I104" s="15">
-        <f>I76-I83-I90</f>
-        <v/>
-      </c>
-      <c r="J104" s="15">
-        <f>J76-J83-J90</f>
-        <v/>
-      </c>
-      <c r="K104" s="15">
-        <f>K76-K83-K90</f>
-        <v/>
-      </c>
-      <c r="L104" s="15">
-        <f>L76-L83-L90</f>
-        <v/>
-      </c>
-      <c r="M104" s="15">
-        <f>M76-M83-M90</f>
-        <v/>
-      </c>
-      <c r="N104" s="15">
-        <f>N76-N83-N90</f>
-        <v/>
-      </c>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="n"/>
+      <c r="H104" s="4" t="n"/>
+      <c r="I104" s="4" t="n"/>
+      <c r="J104" s="4" t="n"/>
+      <c r="K104" s="4" t="n"/>
+      <c r="L104" s="4" t="n"/>
+      <c r="M104" s="4" t="n"/>
+      <c r="N104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Lock-up Test</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr"/>
+          <t>Cash Available for Distribution</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>PASS if DSCR ≥ Lock-up</t>
-        </is>
-      </c>
-      <c r="E105" s="17">
-        <f>IF(E85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="F105" s="17">
-        <f>IF(F85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="G105" s="17">
-        <f>IF(G85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="H105" s="17">
-        <f>IF(H85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="I105" s="17">
-        <f>IF(I85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="J105" s="17">
-        <f>IF(J85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="K105" s="17">
-        <f>IF(K85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="L105" s="17">
-        <f>IF(L85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="M105" s="17">
-        <f>IF(M85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="N105" s="17">
-        <f>IF(N85&gt;=$D$41,"PASS","LOCKED")</f>
+          <t>CFADS - DS - DSRA Fund</t>
+        </is>
+      </c>
+      <c r="E105" s="15">
+        <f>E76-E83-E90</f>
+        <v/>
+      </c>
+      <c r="F105" s="15">
+        <f>F76-F83-F90</f>
+        <v/>
+      </c>
+      <c r="G105" s="15">
+        <f>G76-G83-G90</f>
+        <v/>
+      </c>
+      <c r="H105" s="15">
+        <f>H76-H83-H90</f>
+        <v/>
+      </c>
+      <c r="I105" s="15">
+        <f>I76-I83-I90</f>
+        <v/>
+      </c>
+      <c r="J105" s="15">
+        <f>J76-J83-J90</f>
+        <v/>
+      </c>
+      <c r="K105" s="15">
+        <f>K76-K83-K90</f>
+        <v/>
+      </c>
+      <c r="L105" s="15">
+        <f>L76-L83-L90</f>
+        <v/>
+      </c>
+      <c r="M105" s="15">
+        <f>M76-M83-M90</f>
+        <v/>
+      </c>
+      <c r="N105" s="15">
+        <f>N76-N83-N90</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
+          <t>Lock-up Test</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr"/>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>PASS if DSCR ≥ Lock-up</t>
+        </is>
+      </c>
+      <c r="E106" s="17">
+        <f>IF(E85&gt;=$D$41,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="F106" s="17">
+        <f>IF(F85&gt;=$D$41,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="G106" s="17">
+        <f>IF(G85&gt;=$D$41,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="H106" s="17">
+        <f>IF(H85&gt;=$D$41,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="I106" s="17">
+        <f>IF(I85&gt;=$D$41,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="J106" s="17">
+        <f>IF(J85&gt;=$D$41,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="K106" s="17">
+        <f>IF(K85&gt;=$D$41,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="L106" s="17">
+        <f>IF(L85&gt;=$D$41,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="M106" s="17">
+        <f>IF(M85&gt;=$D$41,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="N106" s="17">
+        <f>IF(N85&gt;=$D$41,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
           <t>Distributable Cash</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>If PASS, MAX(0, Cash Avail)</t>
         </is>
       </c>
-      <c r="E106" s="7">
-        <f>IF(E95="PASS",MAX(0,E94),0)</f>
-        <v/>
-      </c>
-      <c r="F106" s="7">
-        <f>IF(F95="PASS",MAX(0,F94),0)</f>
-        <v/>
-      </c>
-      <c r="G106" s="7">
-        <f>IF(G95="PASS",MAX(0,G94),0)</f>
-        <v/>
-      </c>
-      <c r="H106" s="7">
-        <f>IF(H95="PASS",MAX(0,H94),0)</f>
-        <v/>
-      </c>
-      <c r="I106" s="7">
-        <f>IF(I95="PASS",MAX(0,I94),0)</f>
-        <v/>
-      </c>
-      <c r="J106" s="7">
-        <f>IF(J95="PASS",MAX(0,J94),0)</f>
-        <v/>
-      </c>
-      <c r="K106" s="7">
-        <f>IF(K95="PASS",MAX(0,K94),0)</f>
-        <v/>
-      </c>
-      <c r="L106" s="7">
-        <f>IF(L95="PASS",MAX(0,L94),0)</f>
-        <v/>
-      </c>
-      <c r="M106" s="7">
-        <f>IF(M95="PASS",MAX(0,M94),0)</f>
-        <v/>
-      </c>
-      <c r="N106" s="7">
-        <f>IF(N95="PASS",MAX(0,N94),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr"/>
+      <c r="F107" s="7" t="inlineStr"/>
+      <c r="G107" s="7" t="inlineStr"/>
+      <c r="H107" s="7" t="inlineStr"/>
+      <c r="I107" s="7" t="inlineStr"/>
+      <c r="J107" s="7" t="inlineStr"/>
+      <c r="K107" s="7" t="inlineStr"/>
+      <c r="L107" s="7" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
+      <c r="N107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>SOURCES &amp; USES (Total Construction)</t>
         </is>
       </c>
-      <c r="B108" s="4" t="n"/>
-      <c r="C108" s="4" t="n"/>
-      <c r="D108" s="4" t="n"/>
-      <c r="E108" s="4" t="n"/>
-      <c r="F108" s="4" t="n"/>
-      <c r="G108" s="4" t="n"/>
-      <c r="H108" s="4" t="n"/>
-      <c r="I108" s="4" t="n"/>
-      <c r="J108" s="4" t="n"/>
-      <c r="K108" s="4" t="n"/>
-      <c r="L108" s="4" t="n"/>
-      <c r="M108" s="4" t="n"/>
-      <c r="N108" s="4" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="18" t="inlineStr">
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="4" t="n"/>
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="4" t="n"/>
+      <c r="G109" s="4" t="n"/>
+      <c r="H109" s="4" t="n"/>
+      <c r="I109" s="4" t="n"/>
+      <c r="J109" s="4" t="n"/>
+      <c r="K109" s="4" t="n"/>
+      <c r="L109" s="4" t="n"/>
+      <c r="M109" s="4" t="n"/>
+      <c r="N109" s="4" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="18" t="inlineStr">
         <is>
           <t>USES</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr"/>
-      <c r="C109" s="6" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Development Y0</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B110" s="6" t="inlineStr"/>
       <c r="C110" s="6" t="inlineStr"/>
-      <c r="D110" s="15">
-        <f>$D$17</f>
-        <v/>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Development Y1</t>
+          <t xml:space="preserve">  Development Y0</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -5624,14 +5299,14 @@
       </c>
       <c r="C111" s="6" t="inlineStr"/>
       <c r="D111" s="15">
-        <f>$D$18</f>
+        <f>$D$17</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Construction Y2</t>
+          <t xml:space="preserve">  Development Y1</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
@@ -5641,14 +5316,14 @@
       </c>
       <c r="C112" s="6" t="inlineStr"/>
       <c r="D112" s="15">
-        <f>$D$19</f>
+        <f>$D$18</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Construction Interest</t>
+          <t xml:space="preserve">  Construction Y2</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
@@ -5658,14 +5333,14 @@
       </c>
       <c r="C113" s="6" t="inlineStr"/>
       <c r="D113" s="15">
-        <f>$D$52</f>
+        <f>$D$19</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DSRA Funding (at COD)</t>
+          <t xml:space="preserve">  Construction Interest</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
@@ -5674,58 +5349,56 @@
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr"/>
-      <c r="D114" s="15">
-        <f>G88</f>
-        <v/>
-      </c>
+      <c r="D114" s="15" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  DSRA Funding (at COD)</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr"/>
+      <c r="D115" s="15">
+        <f>G88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
           <t>Total Uses</t>
         </is>
       </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr"/>
-      <c r="D115" s="7">
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr"/>
+      <c r="D116" s="7">
         <f>SUM(D100:D104)</f>
         <v/>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="18" t="inlineStr">
+    <row r="117"/>
+    <row r="118">
+      <c r="A118" s="18" t="inlineStr">
         <is>
           <t>SOURCES</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr"/>
-      <c r="C117" s="6" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Construction Loan</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B118" s="6" t="inlineStr"/>
       <c r="C118" s="6" t="inlineStr"/>
-      <c r="D118" s="15">
-        <f>$D$51</f>
-        <v/>
-      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Term Debt (at COD)</t>
+          <t xml:space="preserve">  Construction Loan</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
@@ -5735,14 +5408,14 @@
       </c>
       <c r="C119" s="6" t="inlineStr"/>
       <c r="D119" s="15">
-        <f>$D$54</f>
+        <f>$D$51</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Equity</t>
+          <t xml:space="preserve">  Term Debt (at COD)</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
@@ -5752,14 +5425,14 @@
       </c>
       <c r="C120" s="6" t="inlineStr"/>
       <c r="D120" s="15">
-        <f>D62</f>
+        <f>$D$54</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Total Sources</t>
+          <t xml:space="preserve">  Total Equity</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
@@ -5768,69 +5441,66 @@
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr"/>
-      <c r="D121" s="7">
-        <f>D109+D110</f>
+      <c r="D121" s="15">
+        <f>D62</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
+          <t>Total Sources</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr"/>
+      <c r="D122" s="7">
+        <f>D109+D110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
           <t>Balance Check</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr"/>
-      <c r="C122" s="6" t="inlineStr"/>
-      <c r="D122" s="10">
+      <c r="B123" s="6" t="inlineStr"/>
+      <c r="C123" s="6" t="inlineStr"/>
+      <c r="D123" s="10">
         <f>IF(ABS(D105-D111)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
+    <row r="124"/>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>EXIT CALCULATIONS</t>
         </is>
       </c>
-      <c r="B124" s="4" t="n"/>
-      <c r="C124" s="4" t="n"/>
-      <c r="D124" s="4" t="n"/>
-      <c r="E124" s="4" t="n"/>
-      <c r="F124" s="4" t="n"/>
-      <c r="G124" s="4" t="n"/>
-      <c r="H124" s="4" t="n"/>
-      <c r="I124" s="4" t="n"/>
-      <c r="J124" s="4" t="n"/>
-      <c r="K124" s="4" t="n"/>
-      <c r="L124" s="4" t="n"/>
-      <c r="M124" s="4" t="n"/>
-      <c r="N124" s="4" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>Cumulative Depreciation</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>Dep × Operating Years</t>
-        </is>
-      </c>
-      <c r="N125" s="15">
-        <f>$D$55*8</f>
-        <v/>
-      </c>
+      <c r="B125" s="4" t="n"/>
+      <c r="C125" s="4" t="n"/>
+      <c r="D125" s="4" t="n"/>
+      <c r="E125" s="4" t="n"/>
+      <c r="F125" s="4" t="n"/>
+      <c r="G125" s="4" t="n"/>
+      <c r="H125" s="4" t="n"/>
+      <c r="I125" s="4" t="n"/>
+      <c r="J125" s="4" t="n"/>
+      <c r="K125" s="4" t="n"/>
+      <c r="L125" s="4" t="n"/>
+      <c r="M125" s="4" t="n"/>
+      <c r="N125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Exit RAB</t>
+          <t>Cumulative Depreciation</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
@@ -5840,18 +5510,18 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>RAB at COD - Cum Dep</t>
+          <t>Dep × Operating Years</t>
         </is>
       </c>
       <c r="N126" s="15">
-        <f>$D$53-N115</f>
+        <f>$D$55*8</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Exit EV</t>
+          <t>Exit RAB</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
@@ -5861,18 +5531,18 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Exit RAB × xRAB Multiple</t>
+          <t>RAB at COD - Cum Dep</t>
         </is>
       </c>
       <c r="N127" s="15">
-        <f>N116*$D$44</f>
+        <f>$D$53-N115</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Exit Debt Payoff</t>
+          <t>Exit EV</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
@@ -5882,18 +5552,15 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Ending Bal at Exit</t>
-        </is>
-      </c>
-      <c r="N128" s="15">
-        <f>N84</f>
-        <v/>
-      </c>
+          <t>Exit RAB × xRAB Multiple</t>
+        </is>
+      </c>
+      <c r="N128" s="15" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>DSRA Release</t>
+          <t>Exit Debt Payoff</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
@@ -5903,232 +5570,210 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>DSRA Ending at Exit</t>
+          <t>Ending Bal at Exit</t>
         </is>
       </c>
       <c r="N129" s="15">
-        <f>N91</f>
+        <f>N84</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
+          <t>DSRA Release</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>DSRA Ending at Exit</t>
+        </is>
+      </c>
+      <c r="N130" s="15">
+        <f>N91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
           <t>Exit Equity Proceeds</t>
         </is>
       </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
         <is>
           <t>Exit EV - Debt + DSRA</t>
         </is>
       </c>
-      <c r="N130" s="7">
-        <f>N117-N118+N119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
+      <c r="N131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132"/>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t>EQUITY RETURNS</t>
         </is>
       </c>
-      <c r="B132" s="4" t="n"/>
-      <c r="C132" s="4" t="n"/>
-      <c r="D132" s="4" t="n"/>
-      <c r="E132" s="4" t="n"/>
-      <c r="F132" s="4" t="n"/>
-      <c r="G132" s="4" t="n"/>
-      <c r="H132" s="4" t="n"/>
-      <c r="I132" s="4" t="n"/>
-      <c r="J132" s="4" t="n"/>
-      <c r="K132" s="4" t="n"/>
-      <c r="L132" s="4" t="n"/>
-      <c r="M132" s="4" t="n"/>
-      <c r="N132" s="4" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>Equity Cash Flow</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr"/>
-      <c r="D133" s="15">
-        <f>-D58</f>
-        <v/>
-      </c>
-      <c r="E133" s="15">
-        <f>-E59</f>
-        <v/>
-      </c>
-      <c r="F133" s="15">
-        <f>-F60</f>
-        <v/>
-      </c>
-      <c r="G133" s="15">
-        <f>-G61-G90+G96</f>
-        <v/>
-      </c>
-      <c r="H133" s="15">
-        <f>H96</f>
-        <v/>
-      </c>
-      <c r="I133" s="15">
-        <f>I96</f>
-        <v/>
-      </c>
-      <c r="J133" s="15">
-        <f>J96</f>
-        <v/>
-      </c>
-      <c r="K133" s="15">
-        <f>K96</f>
-        <v/>
-      </c>
-      <c r="L133" s="15">
-        <f>L96</f>
-        <v/>
-      </c>
-      <c r="M133" s="15">
-        <f>M96</f>
-        <v/>
-      </c>
-      <c r="N133" s="15">
-        <f>N96+N120</f>
-        <v/>
-      </c>
+      <c r="B133" s="4" t="n"/>
+      <c r="C133" s="4" t="n"/>
+      <c r="D133" s="4" t="n"/>
+      <c r="E133" s="4" t="n"/>
+      <c r="F133" s="4" t="n"/>
+      <c r="G133" s="4" t="n"/>
+      <c r="H133" s="4" t="n"/>
+      <c r="I133" s="4" t="n"/>
+      <c r="J133" s="4" t="n"/>
+      <c r="K133" s="4" t="n"/>
+      <c r="L133" s="4" t="n"/>
+      <c r="M133" s="4" t="n"/>
+      <c r="N133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
+          <t>Equity Cash Flow</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr"/>
-      <c r="D134" s="26">
-        <f>IRR(D123:N123)</f>
-        <v/>
-      </c>
+      <c r="D134" s="15" t="inlineStr"/>
+      <c r="E134" s="15" t="inlineStr"/>
+      <c r="F134" s="15" t="inlineStr"/>
+      <c r="G134" s="15" t="inlineStr"/>
+      <c r="H134" s="15" t="inlineStr"/>
+      <c r="I134" s="15" t="inlineStr"/>
+      <c r="J134" s="15" t="inlineStr"/>
+      <c r="K134" s="15" t="inlineStr"/>
+      <c r="L134" s="15" t="inlineStr"/>
+      <c r="M134" s="15" t="inlineStr"/>
+      <c r="N134" s="15" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
+          <t>Levered IRR</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr"/>
+      <c r="D135" s="26" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
           <t>MOIC</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
         <is>
           <t>Sum inflows / outflows</t>
         </is>
       </c>
-      <c r="D135" s="25">
-        <f>SUMIF(D123:N123,"&gt;0")/-SUMIF(D123:N123,"&lt;0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="18" t="inlineStr">
+      <c r="D136" s="25" t="inlineStr"/>
+    </row>
+    <row r="137"/>
+    <row r="138">
+      <c r="A138" s="18" t="inlineStr">
         <is>
           <t>Unlevered Returns (for reference)</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr"/>
-      <c r="C137" s="6" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered Cash Flow</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B138" s="6" t="inlineStr"/>
       <c r="C138" s="6" t="inlineStr"/>
-      <c r="D138" s="15">
-        <f>-$D$17</f>
-        <v/>
-      </c>
-      <c r="E138" s="15">
-        <f>-$D$18</f>
-        <v/>
-      </c>
-      <c r="F138" s="15">
-        <f>-$D$19</f>
-        <v/>
-      </c>
-      <c r="G138" s="15">
-        <f>G76</f>
-        <v/>
-      </c>
-      <c r="H138" s="15">
-        <f>H76</f>
-        <v/>
-      </c>
-      <c r="I138" s="15">
-        <f>I76</f>
-        <v/>
-      </c>
-      <c r="J138" s="15">
-        <f>J76</f>
-        <v/>
-      </c>
-      <c r="K138" s="15">
-        <f>K76</f>
-        <v/>
-      </c>
-      <c r="L138" s="15">
-        <f>L76</f>
-        <v/>
-      </c>
-      <c r="M138" s="15">
-        <f>M76</f>
-        <v/>
-      </c>
-      <c r="N138" s="15">
-        <f>N76+N117</f>
-        <v/>
-      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
+          <t>Unlevered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr"/>
+      <c r="D139" s="15">
+        <f>-$D$17</f>
+        <v/>
+      </c>
+      <c r="E139" s="15">
+        <f>-$D$18</f>
+        <v/>
+      </c>
+      <c r="F139" s="15">
+        <f>-$D$19</f>
+        <v/>
+      </c>
+      <c r="G139" s="15">
+        <f>G76</f>
+        <v/>
+      </c>
+      <c r="H139" s="15">
+        <f>H76</f>
+        <v/>
+      </c>
+      <c r="I139" s="15">
+        <f>I76</f>
+        <v/>
+      </c>
+      <c r="J139" s="15">
+        <f>J76</f>
+        <v/>
+      </c>
+      <c r="K139" s="15">
+        <f>K76</f>
+        <v/>
+      </c>
+      <c r="L139" s="15">
+        <f>L76</f>
+        <v/>
+      </c>
+      <c r="M139" s="15">
+        <f>M76</f>
+        <v/>
+      </c>
+      <c r="N139" s="15">
+        <f>N76+N117</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
           <t>Unlevered IRR</t>
         </is>
       </c>
-      <c r="B139" s="6" t="inlineStr">
+      <c r="B140" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr"/>
-      <c r="D139" s="26">
-        <f>IRR(D128:N128)</f>
-        <v/>
-      </c>
+      <c r="C140" s="6" t="inlineStr"/>
+      <c r="D140" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +97,14 @@
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -154,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,6 +232,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3061,7 +3075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N140"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3143,21 +3157,41 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="inlineStr">
-        <is>
-          <t>═══ DRILL MODE: Key formulas blanked. Rebuild using Formula Logic hints in Column C. ═══</t>
-        </is>
-      </c>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>═══ DRILL MODE - Fill in yellow cells ═══</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>═══ AUDIT STRIP ═══</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>RAB at COD</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="7">
+        <f>$D$63</f>
+        <v/>
+      </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
@@ -3166,13 +3200,17 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
+      <c r="M3" s="51" t="inlineStr">
+        <is>
+          <t>IRR Sensitivity:</t>
+        </is>
+      </c>
       <c r="N3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>RAB at COD</t>
+          <t>Y3 EBITDA (First Op Year)</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3180,218 +3218,241 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
+      </c>
       <c r="D4" s="7">
-        <f>$D$53</f>
-        <v/>
+        <f>G80</f>
+        <v/>
+      </c>
+      <c r="M4" s="52" t="inlineStr">
+        <is>
+          <t>+/- 5% Entry → ~+/- 1% IRR</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Y3 EBITDA (First Op Year)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="44" t="n"/>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+      <c r="M5" s="52" t="inlineStr">
+        <is>
+          <t>+/- 0.5x Exit → ~+/- 1.5% IRR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
-        <is>
-          <t>═══════════ CONTROL PANEL ═══════════</t>
-        </is>
-      </c>
+      <c r="A6" s="44" t="n"/>
       <c r="B6" s="44" t="n"/>
       <c r="C6" s="44" t="n"/>
       <c r="D6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="44" t="n"/>
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
       <c r="B7" s="44" t="n"/>
       <c r="C7" s="44" t="n"/>
       <c r="D7" s="44" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Revenue Mode</t>
         </is>
       </c>
       <c r="B8" s="44" t="n"/>
-      <c r="C8" s="44" t="n"/>
-      <c r="D8" s="44" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Merchant / Contracted / Hybrid</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
-          <t>Revenue Mode</t>
+          <t>Contract End Year</t>
         </is>
       </c>
       <c r="B9" s="44" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D9" s="42" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>Contract End Year</t>
-        </is>
-      </c>
+      <c r="A10" s="44" t="n"/>
       <c r="B10" s="44" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>0 = pure merchant; else year PPA ends</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="n">
-        <v>0</v>
-      </c>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="44" t="n"/>
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
       <c r="B11" s="44" t="n"/>
       <c r="C11" s="44" t="n"/>
       <c r="D11" s="44" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="inlineStr">
-        <is>
-          <t>TIMING</t>
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B12" s="44" t="n"/>
-      <c r="C12" s="44" t="n"/>
-      <c r="D12" s="44" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>Exit Year</t>
+          <t>Tax Credit End Year</t>
         </is>
       </c>
       <c r="B13" s="44" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>5 / 7 / 10</t>
+          <t>0 = N/A; else last year of PTC/ITC</t>
         </is>
       </c>
       <c r="D13" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>Tax Credit End Year</t>
-        </is>
-      </c>
+      <c r="A14" s="44" t="n"/>
       <c r="B14" s="44" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>0 = N/A; else last year of PTC/ITC</t>
-        </is>
-      </c>
-      <c r="D14" s="42" t="n">
-        <v>0</v>
-      </c>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="44" t="n"/>
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
       <c r="B15" s="44" t="n"/>
       <c r="C15" s="44" t="n"/>
-      <c r="D15" s="44" t="n"/>
+      <c r="D15" s="46" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="inlineStr">
-        <is>
-          <t>DEBT</t>
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Debt Sweep</t>
         </is>
       </c>
       <c r="B16" s="44" t="n"/>
-      <c r="C16" s="44" t="n"/>
-      <c r="D16" s="46" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Debt Sweep</t>
+          <t>Sweep %</t>
         </is>
       </c>
       <c r="B17" s="44" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>ON / OFF (for sweep assets)</t>
-        </is>
-      </c>
-      <c r="D17" s="28" t="inlineStr">
-        <is>
-          <t>ON</t>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>Sweep %</t>
-        </is>
-      </c>
+      <c r="A18" s="44" t="n"/>
       <c r="B18" s="44" t="n"/>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Active when Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="47" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="44" t="n"/>
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
       <c r="B19" s="44" t="n"/>
       <c r="C19" s="44" t="n"/>
-      <c r="D19" s="47" t="n"/>
+      <c r="D19" s="48" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="inlineStr">
-        <is>
-          <t>OTHER</t>
+      <c r="A20" s="49" t="inlineStr">
+        <is>
+          <t>Exit Method</t>
         </is>
       </c>
       <c r="B20" s="44" t="n"/>
-      <c r="C20" s="44" t="n"/>
-      <c r="D20" s="48" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Multiple / DCF</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="49" t="inlineStr">
-        <is>
-          <t>Exit Method</t>
-        </is>
-      </c>
-      <c r="B21" s="44" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Multiple / DCF</t>
-        </is>
-      </c>
-      <c r="D21" s="42" t="inlineStr">
-        <is>
-          <t>Multiple</t>
-        </is>
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="10">
+        <f>D112</f>
+        <v/>
       </c>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
@@ -3405,52 +3466,81 @@
       <c r="N21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Debt Payoff Y10</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
       <c r="D22" s="10">
-        <f>D112</f>
+        <f>IF(N84&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Debt Payoff Y10</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr"/>
-      <c r="C23" s="6" t="inlineStr"/>
+          <t>Min DSCR ≥ 1.35x</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
+      </c>
       <c r="D23" s="10">
-        <f>IF(N84&lt;1,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.35,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR ≥ 1.35x</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr"/>
-      <c r="C24" s="6" t="inlineStr"/>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="10" t="n"/>
     </row>
     <row r="25"/>
-    <row r="26"/>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>CONSTRUCTION INPUTS</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>CONSTRUCTION INPUTS</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Development Cost Y0</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Pre-construction dev</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>15</v>
+      </c>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
@@ -3465,7 +3555,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Development Cost Y0</t>
+          <t>Development Cost Y1</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -3475,17 +3565,17 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Pre-construction dev</t>
+          <t>Continued development</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Development Cost Y1</t>
+          <t>Construction Cost Y2</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -3495,63 +3585,78 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Continued development</t>
+          <t>Main construction</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>20</v>
+        <v>550</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Construction Cost Y2</t>
+          <t>COD Year</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Main construction</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>550</v>
+          <t>Commercial operation date</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>COD Year</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Commercial operation date</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32"/>
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="12" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>ASSET INPUTS</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+    </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>ASSET INPUTS</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Transfer Capacity</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Line rating</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>3200</v>
+      </c>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
@@ -3566,73 +3671,88 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Transfer Capacity</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Line rating</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>3200</v>
+          <t>Expected uptime</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Asset Life</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Expected uptime</t>
-        </is>
-      </c>
-      <c r="D35" s="27" t="n">
-        <v>0.98</v>
+          <t>For depreciation</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Asset Life</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>For depreciation</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37"/>
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="12" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>PRICING INPUTS</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+    </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>PRICING INPUTS</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Tariff Rate</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>$/kW-yr</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>FERC-approved</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>32</v>
+      </c>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
@@ -3647,53 +3767,68 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Tariff Rate</t>
+          <t>Tariff Escalation</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>$/kW-yr</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>FERC-approved</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>32</v>
+          <t>Rate increase</t>
+        </is>
+      </c>
+      <c r="D39" s="27" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Tariff Escalation</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>%/yr</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Rate increase</t>
-        </is>
-      </c>
-      <c r="D40" s="27" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="41"/>
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="27" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>COST INPUTS</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
+    </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>COST INPUTS</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>O&amp;M Y3</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Post-COD O&amp;M</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
@@ -3708,53 +3843,68 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>O&amp;M Y3</t>
+          <t>O&amp;M Escalation</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Post-COD O&amp;M</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>3</v>
+          <t>Cost escalation</t>
+        </is>
+      </c>
+      <c r="D43" s="27" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>O&amp;M Escalation</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>%/yr</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Cost escalation</t>
-        </is>
-      </c>
-      <c r="D44" s="27" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="45"/>
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="27" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>FINANCING INPUTS</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="4" t="n"/>
+    </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>FINANCING INPUTS</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Construction Debt %</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Const loan leverage</t>
+        </is>
+      </c>
+      <c r="D46" s="27" t="n">
+        <v>0.85</v>
+      </c>
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
@@ -3769,7 +3919,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Construction Debt %</t>
+          <t>Term Debt % of RAB</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -3779,17 +3929,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Const loan leverage</t>
+          <t>Refi at COD</t>
         </is>
       </c>
       <c r="D47" s="27" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Term Debt % of RAB</t>
+          <t>Interest Rate</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -3799,57 +3949,57 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Refi at COD</t>
+          <t>All-in rate</t>
         </is>
       </c>
       <c r="D48" s="27" t="n">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>DSRA Months</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>All-in rate</t>
-        </is>
-      </c>
-      <c r="D49" s="27" t="n">
-        <v>0.05</v>
+          <t>Debt service reserve</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>DSRA Months</t>
+          <t>Target DSCR</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Debt service reserve</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="n">
-        <v>6</v>
+          <t>For sculpting</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Target DSCR</t>
+          <t>Lock-up DSCR</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -3859,43 +4009,58 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>For sculpting</t>
+          <t>Distribution threshold</t>
         </is>
       </c>
       <c r="D51" s="28" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Lock-up DSCR</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="28" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>EXIT INPUTS</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Exit xRAB Multiple</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Distribution threshold</t>
-        </is>
-      </c>
-      <c r="D52" s="28" t="n">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Exit at RAB multiple</t>
+        </is>
+      </c>
+      <c r="D54" s="28" t="n">
         <v>1.15</v>
       </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>EXIT INPUTS</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
@@ -3910,53 +4075,68 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Exit xRAB Multiple</t>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Exit at RAB multiple</t>
-        </is>
-      </c>
-      <c r="D55" s="28" t="n">
-        <v>1.15</v>
+          <t>Hold period</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>Exit Year</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Hold period</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57"/>
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="12" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>TAX INPUTS</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
+      <c r="K57" s="4" t="n"/>
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="4" t="n"/>
+      <c r="N57" s="4" t="n"/>
+    </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>TAX INPUTS</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Tax Rate</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Blended federal + state</t>
+        </is>
+      </c>
+      <c r="D58" s="27" t="n">
+        <v>0.25</v>
+      </c>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
@@ -3969,35 +4149,51 @@
       <c r="N58" s="4" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Tax Rate</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Blended federal + state</t>
-        </is>
-      </c>
-      <c r="D59" s="27" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="60"/>
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="27" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>CALCULATED ITEMS</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="n"/>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="n"/>
+    </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>CALCULATED ITEMS</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="n"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Construction Loan</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Const Cost × Const Debt %</t>
+        </is>
+      </c>
+      <c r="D61" s="15">
+        <f>$D$29*$D$46</f>
+        <v/>
+      </c>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
@@ -4012,7 +4208,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Construction Loan</t>
+          <t>Construction Interest</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -4022,18 +4218,18 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Const Cost × Const Debt %</t>
+          <t>Capitalized into RAB</t>
         </is>
       </c>
       <c r="D62" s="15">
-        <f>$D$19*$D$36</f>
+        <f>$D$61*$D$48</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Construction Interest</t>
+          <t>RAB at COD</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -4043,15 +4239,18 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Capitalized into RAB</t>
-        </is>
-      </c>
-      <c r="D63" s="15" t="inlineStr"/>
+          <t>Dev + Const + Int</t>
+        </is>
+      </c>
+      <c r="D63" s="15">
+        <f>$D$27+$D$28+$D$29+$D$62</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>RAB at COD</t>
+          <t>Term Debt</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -4061,18 +4260,18 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Dev + Const + Int</t>
+          <t>RAB × Term Debt %</t>
         </is>
       </c>
       <c r="D64" s="15">
-        <f>$D$17+$D$18+$D$19+$D$52</f>
+        <f>$D$63*$D$47</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Term Debt</t>
+          <t>Annual Depreciation</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -4082,45 +4281,56 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>RAB × Term Debt %</t>
+          <t>RAB / Asset Life</t>
         </is>
       </c>
       <c r="D65" s="15">
-        <f>$D$53*$D$37</f>
+        <f>$D$63/$D$35</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>Annual Depreciation</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>RAB / Asset Life</t>
-        </is>
-      </c>
-      <c r="D66" s="15">
-        <f>$D$53/$D$25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67"/>
+      <c r="A66" s="5" t="n"/>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="15" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>CONSTRUCTION PHASE (Y0-Y2)</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="n"/>
+    </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>CONSTRUCTION PHASE (Y0-Y2)</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="n"/>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Development Equity Y0</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="16">
+        <f>$D$27</f>
+        <v/>
+      </c>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
@@ -4135,7 +4345,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Development Equity Y0</t>
+          <t>Development Equity Y1</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -4143,16 +4353,17 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr"/>
-      <c r="D69" s="16">
-        <f>$D$17</f>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="16" t="n"/>
+      <c r="E69" s="16">
+        <f>$D$28</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Development Equity Y1</t>
+          <t>Construction Equity Y2</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -4160,16 +4371,21 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr"/>
-      <c r="E70" s="16">
-        <f>$D$18</f>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Const × (1-Debt%)</t>
+        </is>
+      </c>
+      <c r="E70" s="16" t="n"/>
+      <c r="F70" s="16">
+        <f>$D$29-$D$61</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Construction Equity Y2</t>
+          <t>Refinancing Equity Y3</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -4179,18 +4395,19 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Const × (1-Debt%)</t>
-        </is>
-      </c>
-      <c r="F71" s="16">
-        <f>$D$19*(1-$D$36)</f>
+          <t>Const Loan - Term Debt</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="n"/>
+      <c r="G71" s="16">
+        <f>$D$61-$D$64</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Refinancing Equity Y3</t>
+          <t>Total Equity Invested</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -4198,116 +4415,169 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>Const Loan - Term Debt</t>
-        </is>
-      </c>
-      <c r="G72" s="16">
-        <f>($D$51+$D$52)-$D$54</f>
-        <v/>
-      </c>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="7">
+        <f>D68+E69+F70+G71</f>
+        <v/>
+      </c>
+      <c r="G72" s="16" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Total Equity Invested</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr"/>
-      <c r="D73" s="7">
-        <f>D58+E59+F60+G61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74"/>
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>OPERATING MODEL (Y3+ Post-COD)</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n"/>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="n"/>
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="n"/>
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="n"/>
+      <c r="J74" s="4" t="n"/>
+      <c r="K74" s="4" t="n"/>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="4" t="n"/>
+      <c r="N74" s="4" t="n"/>
+    </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING MODEL (Y3+ Post-COD)</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="n"/>
-      <c r="C75" s="4" t="n"/>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Tariff Rate</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>$/kW-yr</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Escalated</t>
+        </is>
+      </c>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="n"/>
-      <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="n"/>
-      <c r="J75" s="4" t="n"/>
-      <c r="K75" s="4" t="n"/>
-      <c r="L75" s="4" t="n"/>
-      <c r="M75" s="4" t="n"/>
-      <c r="N75" s="4" t="n"/>
+      <c r="E75" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="15">
+        <f>$D$38*(1+$D$39)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="H75" s="15">
+        <f>$D$38*(1+$D$39)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="I75" s="15">
+        <f>$D$38*(1+$D$39)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="J75" s="15">
+        <f>$D$38*(1+$D$39)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="K75" s="15">
+        <f>$D$38*(1+$D$39)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="L75" s="15">
+        <f>$D$38*(1+$D$39)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="M75" s="15">
+        <f>$D$38*(1+$D$39)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="N75" s="15">
+        <f>$D$38*(1+$D$39)^(8-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Tariff Rate</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>$/kW-yr</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Escalated</t>
-        </is>
-      </c>
-      <c r="E76" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F76" s="15">
-        <f>0</f>
-        <v/>
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="E76" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G76" s="15">
-        <f>$D$28*(1+$D$29)^(3-3)</f>
+        <f>$D$33*$D$34*G75/1000</f>
         <v/>
       </c>
       <c r="H76" s="15">
-        <f>$D$28*(1+$D$29)^(4-3)</f>
+        <f>$D$33*$D$34*H75/1000</f>
         <v/>
       </c>
       <c r="I76" s="15">
-        <f>$D$28*(1+$D$29)^(5-3)</f>
+        <f>$D$33*$D$34*I75/1000</f>
         <v/>
       </c>
       <c r="J76" s="15">
-        <f>$D$28*(1+$D$29)^(6-3)</f>
+        <f>$D$33*$D$34*J75/1000</f>
         <v/>
       </c>
       <c r="K76" s="15">
-        <f>$D$28*(1+$D$29)^(7-3)</f>
+        <f>$D$33*$D$34*K75/1000</f>
         <v/>
       </c>
       <c r="L76" s="15">
-        <f>$D$28*(1+$D$29)^(8-3)</f>
+        <f>$D$33*$D$34*L75/1000</f>
         <v/>
       </c>
       <c r="M76" s="15">
-        <f>$D$28*(1+$D$29)^(9-3)</f>
+        <f>$D$33*$D$34*M75/1000</f>
         <v/>
       </c>
       <c r="N76" s="15">
-        <f>$D$28*(1+$D$29)^(10-3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77"/>
+        <f>$D$33*$D$34*N75/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Cap × Tariff × Avail × 1000/1M</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="n"/>
+      <c r="F77" s="15" t="n"/>
+      <c r="G77" s="15" t="n"/>
+      <c r="H77" s="15" t="n"/>
+      <c r="I77" s="15" t="n"/>
+      <c r="J77" s="15" t="n"/>
+      <c r="K77" s="15" t="n"/>
+      <c r="L77" s="15" t="n"/>
+      <c r="M77" s="15" t="n"/>
+      <c r="N77" s="15" t="n"/>
+    </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>O&amp;M Cost</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -4317,126 +4587,213 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Cap × Tariff × Avail × 1000/1M</t>
-        </is>
-      </c>
-      <c r="E78" s="15" t="inlineStr"/>
-      <c r="F78" s="15" t="inlineStr"/>
-      <c r="G78" s="15" t="inlineStr"/>
-      <c r="H78" s="15" t="inlineStr"/>
-      <c r="I78" s="15" t="inlineStr"/>
-      <c r="J78" s="15" t="inlineStr"/>
-      <c r="K78" s="15" t="inlineStr"/>
-      <c r="L78" s="15" t="inlineStr"/>
-      <c r="M78" s="15" t="inlineStr"/>
-      <c r="N78" s="15" t="inlineStr"/>
+          <t>Post-COD only</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="n"/>
+      <c r="F78" s="15" t="n"/>
+      <c r="G78" s="15" t="n"/>
+      <c r="H78" s="15" t="n"/>
+      <c r="I78" s="15" t="n"/>
+      <c r="J78" s="15" t="n"/>
+      <c r="K78" s="15" t="n"/>
+      <c r="L78" s="15" t="n"/>
+      <c r="M78" s="15" t="n"/>
+      <c r="N78" s="15" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>O&amp;M Cost</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="E79" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="53">
+        <f>G76-G77</f>
+        <v/>
+      </c>
+      <c r="H79" s="53">
+        <f>H76-H77</f>
+        <v/>
+      </c>
+      <c r="I79" s="53">
+        <f>I76-I77</f>
+        <v/>
+      </c>
+      <c r="J79" s="53">
+        <f>J76-J77</f>
+        <v/>
+      </c>
+      <c r="K79" s="53">
+        <f>K76-K77</f>
+        <v/>
+      </c>
+      <c r="L79" s="53">
+        <f>L76-L77</f>
+        <v/>
+      </c>
+      <c r="M79" s="53">
+        <f>M76-M77</f>
+        <v/>
+      </c>
+      <c r="N79" s="53">
+        <f>N76-N77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="n"/>
+      <c r="F80" s="7" t="n"/>
+      <c r="G80" s="7" t="n"/>
+      <c r="H80" s="7" t="n"/>
+      <c r="I80" s="7" t="n"/>
+      <c r="J80" s="7" t="n"/>
+      <c r="K80" s="7" t="n"/>
+      <c r="L80" s="7" t="n"/>
+      <c r="M80" s="7" t="n"/>
+      <c r="N80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n"/>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="7" t="n"/>
+      <c r="G81" s="7" t="n"/>
+      <c r="H81" s="7" t="n"/>
+      <c r="I81" s="7" t="n"/>
+      <c r="J81" s="7" t="n"/>
+      <c r="K81" s="7" t="n"/>
+      <c r="L81" s="7" t="n"/>
+      <c r="M81" s="7" t="n"/>
+      <c r="N81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>CASH FLOW</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n"/>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="4">
+        <f>MAX(0,G79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="H82" s="4">
+        <f>MAX(0,H79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="I82" s="4">
+        <f>MAX(0,I79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="J82" s="4">
+        <f>MAX(0,J79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="K82" s="4">
+        <f>MAX(0,K79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="L82" s="4">
+        <f>MAX(0,L79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="M82" s="4">
+        <f>MAX(0,M79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="N82" s="4">
+        <f>MAX(0,N79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>Post-COD only</t>
         </is>
       </c>
-      <c r="E79" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F79" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G79" s="15">
-        <f>$D$32*(1+$D$33)^(3-3)</f>
-        <v/>
-      </c>
-      <c r="H79" s="15">
-        <f>$D$32*(1+$D$33)^(4-3)</f>
-        <v/>
-      </c>
-      <c r="I79" s="15">
-        <f>$D$32*(1+$D$33)^(5-3)</f>
-        <v/>
-      </c>
-      <c r="J79" s="15">
-        <f>$D$32*(1+$D$33)^(6-3)</f>
-        <v/>
-      </c>
-      <c r="K79" s="15">
-        <f>$D$32*(1+$D$33)^(7-3)</f>
-        <v/>
-      </c>
-      <c r="L79" s="15">
-        <f>$D$32*(1+$D$33)^(8-3)</f>
-        <v/>
-      </c>
-      <c r="M79" s="15">
-        <f>$D$32*(1+$D$33)^(9-3)</f>
-        <v/>
-      </c>
-      <c r="N79" s="15">
-        <f>$D$32*(1+$D$33)^(10-3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80"/>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr"/>
-      <c r="E81" s="7" t="inlineStr"/>
-      <c r="F81" s="7" t="inlineStr"/>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr"/>
-      <c r="I81" s="7" t="inlineStr"/>
-      <c r="J81" s="7" t="inlineStr"/>
-      <c r="K81" s="7" t="inlineStr"/>
-      <c r="L81" s="7" t="inlineStr"/>
-      <c r="M81" s="7" t="inlineStr"/>
-      <c r="N81" s="7" t="inlineStr"/>
-    </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>CASH FLOW</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="n"/>
-      <c r="C83" s="4" t="n"/>
       <c r="D83" s="4" t="n"/>
-      <c r="E83" s="4" t="n"/>
-      <c r="F83" s="4" t="n"/>
-      <c r="G83" s="4" t="n"/>
-      <c r="H83" s="4" t="n"/>
-      <c r="I83" s="4" t="n"/>
-      <c r="J83" s="4" t="n"/>
-      <c r="K83" s="4" t="n"/>
-      <c r="L83" s="4" t="n"/>
-      <c r="M83" s="4" t="n"/>
-      <c r="N83" s="4" t="n"/>
+      <c r="E83" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="H83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="I83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="J83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="K83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="L83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="M83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="N83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>EBIT</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -4446,54 +4803,52 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Post-COD only</t>
-        </is>
-      </c>
-      <c r="E84" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F84" s="15">
-        <f>0</f>
-        <v/>
+          <t>EBITDA - Depreciation</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G84" s="15">
-        <f>$D$55</f>
+        <f>G80-G83</f>
         <v/>
       </c>
       <c r="H84" s="15">
-        <f>$D$55</f>
+        <f>H80-H83</f>
         <v/>
       </c>
       <c r="I84" s="15">
-        <f>$D$55</f>
+        <f>I80-I83</f>
         <v/>
       </c>
       <c r="J84" s="15">
-        <f>$D$55</f>
+        <f>J80-J83</f>
         <v/>
       </c>
       <c r="K84" s="15">
-        <f>$D$55</f>
+        <f>K80-K83</f>
         <v/>
       </c>
       <c r="L84" s="15">
-        <f>$D$55</f>
+        <f>L80-L83</f>
         <v/>
       </c>
       <c r="M84" s="15">
-        <f>$D$55</f>
+        <f>M80-M83</f>
         <v/>
       </c>
       <c r="N84" s="15">
-        <f>$D$55</f>
+        <f>N80-N83</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -4503,24 +4858,24 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>EBITDA - Depreciation</t>
-        </is>
-      </c>
-      <c r="E85" s="15" t="inlineStr"/>
-      <c r="F85" s="15" t="inlineStr"/>
-      <c r="G85" s="15" t="inlineStr"/>
-      <c r="H85" s="15" t="inlineStr"/>
-      <c r="I85" s="15" t="inlineStr"/>
-      <c r="J85" s="15" t="inlineStr"/>
-      <c r="K85" s="15" t="inlineStr"/>
-      <c r="L85" s="15" t="inlineStr"/>
-      <c r="M85" s="15" t="inlineStr"/>
-      <c r="N85" s="15" t="inlineStr"/>
+          <t>MAX(0, EBIT) × Tax Rate</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="n"/>
+      <c r="F85" s="15" t="n"/>
+      <c r="G85" s="15" t="n"/>
+      <c r="H85" s="15" t="n"/>
+      <c r="I85" s="15" t="n"/>
+      <c r="J85" s="15" t="n"/>
+      <c r="K85" s="15" t="n"/>
+      <c r="L85" s="15" t="n"/>
+      <c r="M85" s="15" t="n"/>
+      <c r="N85" s="15" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>CFADS</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -4530,72 +4885,144 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, EBIT) × Tax Rate</t>
-        </is>
-      </c>
-      <c r="E86" s="15" t="inlineStr"/>
-      <c r="F86" s="15" t="inlineStr"/>
-      <c r="G86" s="15" t="inlineStr"/>
-      <c r="H86" s="15" t="inlineStr"/>
-      <c r="I86" s="15" t="inlineStr"/>
-      <c r="J86" s="15" t="inlineStr"/>
-      <c r="K86" s="15" t="inlineStr"/>
-      <c r="L86" s="15" t="inlineStr"/>
-      <c r="M86" s="15" t="inlineStr"/>
-      <c r="N86" s="15" t="inlineStr"/>
+          <t>EBITDA - Taxes</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="n"/>
+      <c r="F86" s="7" t="n"/>
+      <c r="G86" s="7" t="n"/>
+      <c r="H86" s="7" t="n"/>
+      <c r="I86" s="7" t="n"/>
+      <c r="J86" s="7" t="n"/>
+      <c r="K86" s="7" t="n"/>
+      <c r="L86" s="7" t="n"/>
+      <c r="M86" s="7" t="n"/>
+      <c r="N86" s="7" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>CFADS</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA - Taxes</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr"/>
-      <c r="F87" s="7" t="inlineStr"/>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
-      <c r="J87" s="7" t="inlineStr"/>
-      <c r="K87" s="7" t="inlineStr"/>
-      <c r="L87" s="7" t="inlineStr"/>
-      <c r="M87" s="7" t="inlineStr"/>
-      <c r="N87" s="7" t="inlineStr"/>
-    </row>
-    <row r="88"/>
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="7">
+        <f>$D$64</f>
+        <v/>
+      </c>
+      <c r="H87" s="7">
+        <f>G92</f>
+        <v/>
+      </c>
+      <c r="I87" s="7">
+        <f>H92</f>
+        <v/>
+      </c>
+      <c r="J87" s="7">
+        <f>I92</f>
+        <v/>
+      </c>
+      <c r="K87" s="7">
+        <f>J92</f>
+        <v/>
+      </c>
+      <c r="L87" s="7">
+        <f>K92</f>
+        <v/>
+      </c>
+      <c r="M87" s="7">
+        <f>L92</f>
+        <v/>
+      </c>
+      <c r="N87" s="7">
+        <f>M92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>DEBT SCHEDULE (Sculpted 1.40x, Y3+ Only)</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="n"/>
+      <c r="C88" s="4" t="n"/>
+      <c r="D88" s="4" t="n"/>
+      <c r="E88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="4">
+        <f>G87*$D$48</f>
+        <v/>
+      </c>
+      <c r="H88" s="4">
+        <f>H87*$D$48</f>
+        <v/>
+      </c>
+      <c r="I88" s="4">
+        <f>I87*$D$48</f>
+        <v/>
+      </c>
+      <c r="J88" s="4">
+        <f>J87*$D$48</f>
+        <v/>
+      </c>
+      <c r="K88" s="4">
+        <f>K87*$D$48</f>
+        <v/>
+      </c>
+      <c r="L88" s="4">
+        <f>L87*$D$48</f>
+        <v/>
+      </c>
+      <c r="M88" s="4">
+        <f>M87*$D$48</f>
+        <v/>
+      </c>
+      <c r="N88" s="4">
+        <f>N87*$D$48</f>
+        <v/>
+      </c>
+    </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>DEBT SCHEDULE (Sculpted 1.40x, Y3+ Only)</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="n"/>
-      <c r="C89" s="4" t="n"/>
-      <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="n"/>
-      <c r="F89" s="4" t="n"/>
-      <c r="G89" s="4" t="n"/>
-      <c r="H89" s="4" t="n"/>
-      <c r="I89" s="4" t="n"/>
-      <c r="J89" s="4" t="n"/>
-      <c r="K89" s="4" t="n"/>
-      <c r="L89" s="4" t="n"/>
-      <c r="M89" s="4" t="n"/>
-      <c r="N89" s="4" t="n"/>
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Beginning Balance</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="15" t="n"/>
+      <c r="F89" s="15" t="n"/>
+      <c r="G89" s="15" t="n"/>
+      <c r="H89" s="15" t="n"/>
+      <c r="I89" s="15" t="n"/>
+      <c r="J89" s="15" t="n"/>
+      <c r="K89" s="15" t="n"/>
+      <c r="L89" s="15" t="n"/>
+      <c r="M89" s="15" t="n"/>
+      <c r="N89" s="15" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Beginning Balance</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -4603,52 +5030,26 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr"/>
-      <c r="E90" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F90" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G90" s="15">
-        <f>$D$54</f>
-        <v/>
-      </c>
-      <c r="H90" s="15">
-        <f>G84</f>
-        <v/>
-      </c>
-      <c r="I90" s="15">
-        <f>H84</f>
-        <v/>
-      </c>
-      <c r="J90" s="15">
-        <f>I84</f>
-        <v/>
-      </c>
-      <c r="K90" s="15">
-        <f>J84</f>
-        <v/>
-      </c>
-      <c r="L90" s="15">
-        <f>K84</f>
-        <v/>
-      </c>
-      <c r="M90" s="15">
-        <f>L84</f>
-        <v/>
-      </c>
-      <c r="N90" s="15">
-        <f>M84</f>
-        <v/>
-      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Beg Bal × Int Rate</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="n"/>
+      <c r="F90" s="15" t="n"/>
+      <c r="G90" s="15" t="n"/>
+      <c r="H90" s="15" t="n"/>
+      <c r="I90" s="15" t="n"/>
+      <c r="J90" s="15" t="n"/>
+      <c r="K90" s="15" t="n"/>
+      <c r="L90" s="15" t="n"/>
+      <c r="M90" s="15" t="n"/>
+      <c r="N90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Target Debt Service</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -4658,24 +5059,24 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Beg Bal × Int Rate</t>
-        </is>
-      </c>
-      <c r="E91" s="15" t="inlineStr"/>
-      <c r="F91" s="15" t="inlineStr"/>
-      <c r="G91" s="15" t="inlineStr"/>
-      <c r="H91" s="15" t="inlineStr"/>
-      <c r="I91" s="15" t="inlineStr"/>
-      <c r="J91" s="15" t="inlineStr"/>
-      <c r="K91" s="15" t="inlineStr"/>
-      <c r="L91" s="15" t="inlineStr"/>
-      <c r="M91" s="15" t="inlineStr"/>
-      <c r="N91" s="15" t="inlineStr"/>
+          <t>CFADS / Target DSCR</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="n"/>
+      <c r="F91" s="15" t="n"/>
+      <c r="G91" s="15" t="n"/>
+      <c r="H91" s="15" t="n"/>
+      <c r="I91" s="15" t="n"/>
+      <c r="J91" s="15" t="n"/>
+      <c r="K91" s="15" t="n"/>
+      <c r="L91" s="15" t="n"/>
+      <c r="M91" s="15" t="n"/>
+      <c r="N91" s="15" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Target Debt Service</t>
+          <t>Sculpted Principal</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -4685,24 +5086,24 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>CFADS / Target DSCR</t>
-        </is>
-      </c>
-      <c r="E92" s="15" t="inlineStr"/>
-      <c r="F92" s="15" t="inlineStr"/>
-      <c r="G92" s="15" t="inlineStr"/>
-      <c r="H92" s="15" t="inlineStr"/>
-      <c r="I92" s="15" t="inlineStr"/>
-      <c r="J92" s="15" t="inlineStr"/>
-      <c r="K92" s="15" t="inlineStr"/>
-      <c r="L92" s="15" t="inlineStr"/>
-      <c r="M92" s="15" t="inlineStr"/>
-      <c r="N92" s="15" t="inlineStr"/>
+          <t>Target DS - Interest</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="n"/>
+      <c r="F92" s="15" t="n"/>
+      <c r="G92" s="15" t="n"/>
+      <c r="H92" s="15" t="n"/>
+      <c r="I92" s="15" t="n"/>
+      <c r="J92" s="15" t="n"/>
+      <c r="K92" s="15" t="n"/>
+      <c r="L92" s="15" t="n"/>
+      <c r="M92" s="15" t="n"/>
+      <c r="N92" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Sculpted Principal</t>
+          <t>Actual Debt Service</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -4712,24 +5113,24 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Target DS - Interest</t>
-        </is>
-      </c>
-      <c r="E93" s="15" t="inlineStr"/>
-      <c r="F93" s="15" t="inlineStr"/>
-      <c r="G93" s="15" t="inlineStr"/>
-      <c r="H93" s="15" t="inlineStr"/>
-      <c r="I93" s="15" t="inlineStr"/>
-      <c r="J93" s="15" t="inlineStr"/>
-      <c r="K93" s="15" t="inlineStr"/>
-      <c r="L93" s="15" t="inlineStr"/>
-      <c r="M93" s="15" t="inlineStr"/>
-      <c r="N93" s="15" t="inlineStr"/>
+          <t>Interest + Principal</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="n"/>
+      <c r="F93" s="15" t="n"/>
+      <c r="G93" s="54" t="n"/>
+      <c r="H93" s="54" t="n"/>
+      <c r="I93" s="54" t="n"/>
+      <c r="J93" s="54" t="n"/>
+      <c r="K93" s="54" t="n"/>
+      <c r="L93" s="54" t="n"/>
+      <c r="M93" s="54" t="n"/>
+      <c r="N93" s="54" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Actual Debt Service</t>
+          <t>Ending Balance</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -4739,129 +5140,170 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>Interest + Principal</t>
-        </is>
-      </c>
-      <c r="E94" s="15">
-        <f>E80+E82</f>
-        <v/>
-      </c>
-      <c r="F94" s="15">
-        <f>F80+F82</f>
-        <v/>
-      </c>
-      <c r="G94" s="15">
-        <f>G80+G82</f>
-        <v/>
-      </c>
-      <c r="H94" s="15">
-        <f>H80+H82</f>
-        <v/>
-      </c>
-      <c r="I94" s="15">
-        <f>I80+I82</f>
-        <v/>
-      </c>
-      <c r="J94" s="15">
-        <f>J80+J82</f>
-        <v/>
-      </c>
-      <c r="K94" s="15">
-        <f>K80+K82</f>
-        <v/>
-      </c>
-      <c r="L94" s="15">
-        <f>L80+L82</f>
-        <v/>
-      </c>
-      <c r="M94" s="15">
-        <f>M80+M82</f>
-        <v/>
-      </c>
-      <c r="N94" s="15">
-        <f>N80+N82</f>
-        <v/>
-      </c>
+          <t>Beg - Principal</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="n"/>
+      <c r="F94" s="15" t="n"/>
+      <c r="G94" s="15" t="n"/>
+      <c r="H94" s="15" t="n"/>
+      <c r="I94" s="15" t="n"/>
+      <c r="J94" s="15" t="n"/>
+      <c r="K94" s="15" t="n"/>
+      <c r="L94" s="15" t="n"/>
+      <c r="M94" s="15" t="n"/>
+      <c r="N94" s="15" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Ending Balance</t>
+          <t>Actual DSCR</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Beg - Principal</t>
-        </is>
-      </c>
-      <c r="E95" s="15" t="inlineStr"/>
-      <c r="F95" s="15" t="inlineStr"/>
-      <c r="G95" s="15" t="inlineStr"/>
-      <c r="H95" s="15" t="inlineStr"/>
-      <c r="I95" s="15" t="inlineStr"/>
-      <c r="J95" s="15" t="inlineStr"/>
-      <c r="K95" s="15" t="inlineStr"/>
-      <c r="L95" s="15" t="inlineStr"/>
-      <c r="M95" s="15" t="inlineStr"/>
-      <c r="N95" s="15" t="inlineStr"/>
+          <t>CFADS / Actual DS</t>
+        </is>
+      </c>
+      <c r="E95" s="25" t="n"/>
+      <c r="F95" s="25" t="n"/>
+      <c r="G95" s="25" t="n"/>
+      <c r="H95" s="25" t="n"/>
+      <c r="I95" s="25" t="n"/>
+      <c r="J95" s="25" t="n"/>
+      <c r="K95" s="25" t="n"/>
+      <c r="L95" s="25" t="n"/>
+      <c r="M95" s="25" t="n"/>
+      <c r="N95" s="25" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Actual DSCR</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>CFADS / Actual DS</t>
-        </is>
-      </c>
-      <c r="E96" s="25" t="inlineStr"/>
-      <c r="F96" s="25" t="inlineStr"/>
-      <c r="G96" s="25" t="inlineStr"/>
-      <c r="H96" s="25" t="inlineStr"/>
-      <c r="I96" s="25" t="inlineStr"/>
-      <c r="J96" s="25" t="inlineStr"/>
-      <c r="K96" s="25" t="inlineStr"/>
-      <c r="L96" s="25" t="inlineStr"/>
-      <c r="M96" s="25" t="inlineStr"/>
-      <c r="N96" s="25" t="inlineStr"/>
-    </row>
-    <row r="97"/>
+      <c r="A96" s="5" t="n"/>
+      <c r="B96" s="6" t="n"/>
+      <c r="C96" s="6" t="n"/>
+      <c r="E96" s="25" t="n"/>
+      <c r="F96" s="25" t="n"/>
+      <c r="G96" s="25" t="n"/>
+      <c r="H96" s="25" t="n"/>
+      <c r="I96" s="25" t="n"/>
+      <c r="J96" s="25" t="n"/>
+      <c r="K96" s="25" t="n"/>
+      <c r="L96" s="25" t="n"/>
+      <c r="M96" s="25" t="n"/>
+      <c r="N96" s="25" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>DSRA (Debt Service Reserve Account)</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4">
+        <f>H91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="H97" s="4">
+        <f>I91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="I97" s="4">
+        <f>J91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="J97" s="4">
+        <f>K91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="K97" s="4">
+        <f>L91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="L97" s="4">
+        <f>M91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="M97" s="4">
+        <f>N91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="N97" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>DSRA (Debt Service Reserve Account)</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="n"/>
-      <c r="C98" s="4" t="n"/>
-      <c r="D98" s="4" t="n"/>
-      <c r="E98" s="4" t="n"/>
-      <c r="F98" s="4" t="n"/>
-      <c r="G98" s="4" t="n"/>
-      <c r="H98" s="4" t="n"/>
-      <c r="I98" s="4" t="n"/>
-      <c r="J98" s="4" t="n"/>
-      <c r="K98" s="4" t="n"/>
-      <c r="L98" s="4" t="n"/>
-      <c r="M98" s="4" t="n"/>
-      <c r="N98" s="4" t="n"/>
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>DSRA Target</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Next Yr DS × DSRA Months / 12</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="15">
+        <f>H93*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="H98" s="15">
+        <f>I93*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="I98" s="15">
+        <f>J93*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="J98" s="15">
+        <f>K93*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="K98" s="15">
+        <f>L93*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="L98" s="15">
+        <f>M93*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="M98" s="15">
+        <f>N93*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="N98" s="15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>DSRA Target</t>
+          <t>DSRA Beginning</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -4869,60 +5311,53 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>Next Yr DS × DSRA Months / 12</t>
-        </is>
-      </c>
-      <c r="D99" s="15">
-        <f>G83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="E99" s="15">
-        <f>G83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="F99" s="15">
-        <f>G83*$D$39/12</f>
-        <v/>
+      <c r="C99" s="6" t="n"/>
+      <c r="D99" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G99" s="15">
-        <f>H83*$D$39/12</f>
+        <f>D114</f>
         <v/>
       </c>
       <c r="H99" s="15">
-        <f>I83*$D$39/12</f>
+        <f>G101</f>
         <v/>
       </c>
       <c r="I99" s="15">
-        <f>J83*$D$39/12</f>
+        <f>H101</f>
         <v/>
       </c>
       <c r="J99" s="15">
-        <f>K83*$D$39/12</f>
+        <f>I101</f>
         <v/>
       </c>
       <c r="K99" s="15">
-        <f>L83*$D$39/12</f>
+        <f>J101</f>
         <v/>
       </c>
       <c r="L99" s="15">
-        <f>M83*$D$39/12</f>
+        <f>K101</f>
         <v/>
       </c>
       <c r="M99" s="15">
-        <f>N83*$D$39/12</f>
+        <f>L101</f>
         <v/>
       </c>
       <c r="N99" s="15">
-        <f>0</f>
+        <f>M101</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>DSRA Beginning</t>
+          <t>DSRA Funding/(Release)</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -4930,56 +5365,58 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr"/>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Target - Beginning</t>
+        </is>
+      </c>
       <c r="D100" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E100" s="15">
-        <f>D91</f>
-        <v/>
-      </c>
-      <c r="F100" s="15">
-        <f>E91</f>
-        <v/>
+        <f>D88-D89</f>
+        <v/>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G100" s="15">
-        <f>F91</f>
+        <f>G98-G99</f>
         <v/>
       </c>
       <c r="H100" s="15">
-        <f>G91</f>
+        <f>H98-H99</f>
         <v/>
       </c>
       <c r="I100" s="15">
-        <f>H91</f>
+        <f>I98-I99</f>
         <v/>
       </c>
       <c r="J100" s="15">
-        <f>I91</f>
+        <f>J98-J99</f>
         <v/>
       </c>
       <c r="K100" s="15">
-        <f>J91</f>
+        <f>K98-K99</f>
         <v/>
       </c>
       <c r="L100" s="15">
-        <f>K91</f>
+        <f>L98-L99</f>
         <v/>
       </c>
       <c r="M100" s="15">
-        <f>L91</f>
+        <f>M98-M99</f>
         <v/>
       </c>
       <c r="N100" s="15">
-        <f>M91</f>
+        <f>N98-N99</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>DSRA Funding/(Release)</t>
+          <t>DSRA Ending</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -4989,283 +5426,329 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Target - Beginning</t>
+          <t>Beginning + Funding</t>
         </is>
       </c>
       <c r="D101" s="15">
-        <f>D88-D89</f>
-        <v/>
-      </c>
-      <c r="E101" s="15">
-        <f>E88-E89</f>
-        <v/>
-      </c>
-      <c r="F101" s="15">
-        <f>F88-F89</f>
-        <v/>
+        <f>D89+D90</f>
+        <v/>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G101" s="15">
-        <f>G88-G89</f>
+        <f>G99+G100</f>
         <v/>
       </c>
       <c r="H101" s="15">
-        <f>H88-H89</f>
+        <f>H99+H100</f>
         <v/>
       </c>
       <c r="I101" s="15">
-        <f>I88-I89</f>
+        <f>I99+I100</f>
         <v/>
       </c>
       <c r="J101" s="15">
-        <f>J88-J89</f>
+        <f>J99+J100</f>
         <v/>
       </c>
       <c r="K101" s="15">
-        <f>K88-K89</f>
+        <f>K99+K100</f>
         <v/>
       </c>
       <c r="L101" s="15">
-        <f>L88-L89</f>
+        <f>L99+L100</f>
         <v/>
       </c>
       <c r="M101" s="15">
-        <f>M88-M89</f>
+        <f>M99+M100</f>
         <v/>
       </c>
       <c r="N101" s="15">
-        <f>N88-N89</f>
+        <f>N99+N100</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>DSRA Ending</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>Beginning + Funding</t>
-        </is>
-      </c>
-      <c r="D102" s="15">
-        <f>D89+D90</f>
-        <v/>
-      </c>
-      <c r="E102" s="15">
-        <f>E89+E90</f>
-        <v/>
-      </c>
-      <c r="F102" s="15">
-        <f>F89+F90</f>
-        <v/>
-      </c>
-      <c r="G102" s="15">
-        <f>G89+G90</f>
-        <v/>
-      </c>
-      <c r="H102" s="15">
-        <f>H89+H90</f>
-        <v/>
-      </c>
-      <c r="I102" s="15">
-        <f>I89+I90</f>
-        <v/>
-      </c>
-      <c r="J102" s="15">
-        <f>J89+J90</f>
-        <v/>
-      </c>
-      <c r="K102" s="15">
-        <f>K89+K90</f>
-        <v/>
-      </c>
-      <c r="L102" s="15">
-        <f>L89+L90</f>
-        <v/>
-      </c>
-      <c r="M102" s="15">
-        <f>M89+M90</f>
-        <v/>
-      </c>
-      <c r="N102" s="15">
-        <f>N89+N90</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103"/>
+      <c r="A102" s="5" t="n"/>
+      <c r="B102" s="6" t="n"/>
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="15" t="n"/>
+      <c r="E102" s="15" t="n"/>
+      <c r="F102" s="15" t="n"/>
+      <c r="G102" s="15" t="n"/>
+      <c r="H102" s="15" t="n"/>
+      <c r="I102" s="15" t="n"/>
+      <c r="J102" s="15" t="n"/>
+      <c r="K102" s="15" t="n"/>
+      <c r="L102" s="15" t="n"/>
+      <c r="M102" s="15" t="n"/>
+      <c r="N102" s="15" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTION WATERFALL</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4">
+        <f>G83-G91-G99</f>
+        <v/>
+      </c>
+      <c r="H103" s="4">
+        <f>H83-H91-H99</f>
+        <v/>
+      </c>
+      <c r="I103" s="4">
+        <f>I83-I91-I99</f>
+        <v/>
+      </c>
+      <c r="J103" s="4">
+        <f>J83-J91-J99</f>
+        <v/>
+      </c>
+      <c r="K103" s="4">
+        <f>K83-K91-K99</f>
+        <v/>
+      </c>
+      <c r="L103" s="4">
+        <f>L83-L91-L99</f>
+        <v/>
+      </c>
+      <c r="M103" s="4">
+        <f>M83-M91-M99</f>
+        <v/>
+      </c>
+      <c r="N103" s="4">
+        <f>N83-N91-N99</f>
+        <v/>
+      </c>
+    </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTION WATERFALL</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="n"/>
-      <c r="C104" s="4" t="n"/>
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Cash Available for Distribution</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>CFADS - DS - DSRA Fund</t>
+        </is>
+      </c>
       <c r="D104" s="4" t="n"/>
-      <c r="E104" s="4" t="n"/>
-      <c r="F104" s="4" t="n"/>
-      <c r="G104" s="4" t="n"/>
-      <c r="H104" s="4" t="n"/>
-      <c r="I104" s="4" t="n"/>
-      <c r="J104" s="4" t="n"/>
-      <c r="K104" s="4" t="n"/>
-      <c r="L104" s="4" t="n"/>
-      <c r="M104" s="4" t="n"/>
-      <c r="N104" s="4" t="n"/>
+      <c r="E104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="15">
+        <f>G86-G93-G100</f>
+        <v/>
+      </c>
+      <c r="H104" s="15">
+        <f>H86-H93-H100</f>
+        <v/>
+      </c>
+      <c r="I104" s="15">
+        <f>I86-I93-I100</f>
+        <v/>
+      </c>
+      <c r="J104" s="15">
+        <f>J86-J93-J100</f>
+        <v/>
+      </c>
+      <c r="K104" s="15">
+        <f>K86-K93-K100</f>
+        <v/>
+      </c>
+      <c r="L104" s="15">
+        <f>L86-L93-L100</f>
+        <v/>
+      </c>
+      <c r="M104" s="15">
+        <f>M86-M93-M100</f>
+        <v/>
+      </c>
+      <c r="N104" s="15">
+        <f>N86-N93-N100</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Cash Available for Distribution</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+          <t>Lock-up Test</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="n"/>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>CFADS - DS - DSRA Fund</t>
-        </is>
-      </c>
-      <c r="E105" s="15">
-        <f>E76-E83-E90</f>
-        <v/>
-      </c>
-      <c r="F105" s="15">
-        <f>F76-F83-F90</f>
-        <v/>
-      </c>
-      <c r="G105" s="15">
-        <f>G76-G83-G90</f>
-        <v/>
-      </c>
-      <c r="H105" s="15">
-        <f>H76-H83-H90</f>
-        <v/>
-      </c>
-      <c r="I105" s="15">
-        <f>I76-I83-I90</f>
-        <v/>
-      </c>
-      <c r="J105" s="15">
-        <f>J76-J83-J90</f>
-        <v/>
-      </c>
-      <c r="K105" s="15">
-        <f>K76-K83-K90</f>
-        <v/>
-      </c>
-      <c r="L105" s="15">
-        <f>L76-L83-L90</f>
-        <v/>
-      </c>
-      <c r="M105" s="15">
-        <f>M76-M83-M90</f>
-        <v/>
-      </c>
-      <c r="N105" s="15">
-        <f>N76-N83-N90</f>
+          <t>PASS if DSCR ≥ Lock-up</t>
+        </is>
+      </c>
+      <c r="E105" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F105" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G105" s="17">
+        <f>IF(G95&gt;=$D$51,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="H105" s="17">
+        <f>IF(H95&gt;=$D$51,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="I105" s="17">
+        <f>IF(I95&gt;=$D$51,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="J105" s="17">
+        <f>IF(J95&gt;=$D$51,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="K105" s="17">
+        <f>IF(K95&gt;=$D$51,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="L105" s="17">
+        <f>IF(L95&gt;=$D$51,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="M105" s="17">
+        <f>IF(M95&gt;=$D$51,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="N105" s="17">
+        <f>IF(N95&gt;=$D$51,"PASS","LOCKED")</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Lock-up Test</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr"/>
+          <t>Distributable Cash</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>PASS if DSCR ≥ Lock-up</t>
-        </is>
-      </c>
-      <c r="E106" s="17">
-        <f>IF(E85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="F106" s="17">
-        <f>IF(F85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="G106" s="17">
-        <f>IF(G85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="H106" s="17">
-        <f>IF(H85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="I106" s="17">
-        <f>IF(I85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="J106" s="17">
-        <f>IF(J85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="K106" s="17">
-        <f>IF(K85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="L106" s="17">
-        <f>IF(L85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="M106" s="17">
-        <f>IF(M85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="N106" s="17">
-        <f>IF(N85&gt;=$D$41,"PASS","LOCKED")</f>
+          <t>If PASS, MAX(0, Cash Avail)</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="7">
+        <f>IF(G105="PASS",MAX(0,G104),0)</f>
+        <v/>
+      </c>
+      <c r="H106" s="7">
+        <f>IF(H105="PASS",MAX(0,H104),0)</f>
+        <v/>
+      </c>
+      <c r="I106" s="7">
+        <f>IF(I105="PASS",MAX(0,I104),0)</f>
+        <v/>
+      </c>
+      <c r="J106" s="7">
+        <f>IF(J105="PASS",MAX(0,J104),0)</f>
+        <v/>
+      </c>
+      <c r="K106" s="7">
+        <f>IF(K105="PASS",MAX(0,K104),0)</f>
+        <v/>
+      </c>
+      <c r="L106" s="7">
+        <f>IF(L105="PASS",MAX(0,L104),0)</f>
+        <v/>
+      </c>
+      <c r="M106" s="7">
+        <f>IF(M105="PASS",MAX(0,M104),0)</f>
+        <v/>
+      </c>
+      <c r="N106" s="7">
+        <f>IF(N105="PASS",MAX(0,N104),0)</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Distributable Cash</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>If PASS, MAX(0, Cash Avail)</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr"/>
-      <c r="F107" s="7" t="inlineStr"/>
-      <c r="G107" s="7" t="inlineStr"/>
-      <c r="H107" s="7" t="inlineStr"/>
-      <c r="I107" s="7" t="inlineStr"/>
-      <c r="J107" s="7" t="inlineStr"/>
-      <c r="K107" s="7" t="inlineStr"/>
-      <c r="L107" s="7" t="inlineStr"/>
-      <c r="M107" s="7" t="inlineStr"/>
-      <c r="N107" s="7" t="inlineStr"/>
-    </row>
-    <row r="108"/>
+      <c r="A107" s="5" t="n"/>
+      <c r="B107" s="6" t="n"/>
+      <c r="C107" s="6" t="n"/>
+      <c r="E107" s="7" t="n"/>
+      <c r="F107" s="7" t="n"/>
+      <c r="G107" s="7" t="n"/>
+      <c r="H107" s="7" t="n"/>
+      <c r="I107" s="7" t="n"/>
+      <c r="J107" s="7" t="n"/>
+      <c r="K107" s="7" t="n"/>
+      <c r="L107" s="7" t="n"/>
+      <c r="M107" s="7" t="n"/>
+      <c r="N107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>SOURCES &amp; USES (Total Construction)</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="n"/>
+      <c r="C108" s="4" t="n"/>
+      <c r="D108" s="4" t="n"/>
+      <c r="E108" s="4" t="n"/>
+      <c r="F108" s="4" t="n"/>
+      <c r="G108" s="4" t="n"/>
+      <c r="H108" s="4" t="n"/>
+      <c r="I108" s="4" t="n"/>
+      <c r="J108" s="4" t="n"/>
+      <c r="K108" s="4" t="n"/>
+      <c r="L108" s="4" t="n"/>
+      <c r="M108" s="4" t="n"/>
+      <c r="N108" s="4" t="n"/>
+    </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>SOURCES &amp; USES (Total Construction)</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="n"/>
-      <c r="C109" s="4" t="n"/>
-      <c r="D109" s="4" t="n"/>
+      <c r="A109" s="18" t="inlineStr">
+        <is>
+          <t>USES</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="n"/>
+      <c r="C109" s="6" t="n"/>
+      <c r="D109" s="4">
+        <f>$D$27+$D$28+$D$29+$D$62</f>
+        <v/>
+      </c>
       <c r="E109" s="4" t="n"/>
       <c r="F109" s="4" t="n"/>
       <c r="G109" s="4" t="n"/>
@@ -5278,18 +5761,26 @@
       <c r="N109" s="4" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="18" t="inlineStr">
-        <is>
-          <t>USES</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr"/>
-      <c r="C110" s="6" t="inlineStr"/>
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Development Y0</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="15">
+        <f>$D$27</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Development Y0</t>
+          <t xml:space="preserve">  Development Y1</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -5297,16 +5788,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr"/>
+      <c r="C111" s="6" t="n"/>
       <c r="D111" s="15">
-        <f>$D$17</f>
+        <f>$D$28</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Development Y1</t>
+          <t xml:space="preserve">  Construction Y2</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
@@ -5314,16 +5805,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr"/>
+      <c r="C112" s="6" t="n"/>
       <c r="D112" s="15">
-        <f>$D$18</f>
+        <f>$D$29</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Construction Y2</t>
+          <t xml:space="preserve">  Construction Interest</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
@@ -5331,16 +5822,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr"/>
+      <c r="C113" s="6" t="n"/>
       <c r="D113" s="15">
-        <f>$D$19</f>
+        <f>$D$62</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Construction Interest</t>
+          <t xml:space="preserve">  DSRA Funding (at COD)</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
@@ -5348,13 +5839,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr"/>
-      <c r="D114" s="15" t="inlineStr"/>
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="15">
+        <f>G98</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DSRA Funding (at COD)</t>
+          <t>Total Uses</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
@@ -5362,43 +5856,52 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C115" s="6" t="inlineStr"/>
-      <c r="D115" s="15">
-        <f>G88</f>
+      <c r="C115" s="6" t="n"/>
+      <c r="D115" s="7">
+        <f>D110+D111+D112+D113+D114</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>Total Uses</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr"/>
-      <c r="D116" s="7">
-        <f>SUM(D100:D104)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117"/>
+      <c r="A116" s="5" t="n"/>
+      <c r="B116" s="6" t="n"/>
+      <c r="C116" s="6" t="n"/>
+      <c r="D116" s="7" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="18" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="n"/>
+      <c r="C117" s="6" t="n"/>
+      <c r="D117">
+        <f>IF(ABS(D111-D115)&lt;0.01,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
     <row r="118">
-      <c r="A118" s="18" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr"/>
-      <c r="C118" s="6" t="inlineStr"/>
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Construction Loan</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="n"/>
+      <c r="D118" s="15">
+        <f>$D$61</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Construction Loan</t>
+          <t xml:space="preserve">  Term Debt (at COD)</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
@@ -5406,16 +5909,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C119" s="6" t="inlineStr"/>
+      <c r="C119" s="6" t="n"/>
       <c r="D119" s="15">
-        <f>$D$51</f>
+        <f>$D$64</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Term Debt (at COD)</t>
+          <t xml:space="preserve">  Total Equity</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
@@ -5423,16 +5926,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr"/>
+      <c r="C120" s="6" t="n"/>
       <c r="D120" s="15">
-        <f>$D$54</f>
+        <f>D115-D118-D119+D118</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Equity</t>
+          <t>Total Sources</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
@@ -5440,52 +5943,77 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr"/>
-      <c r="D121" s="15">
-        <f>D62</f>
+      <c r="C121" s="6" t="n"/>
+      <c r="D121" s="7">
+        <f>D119+D120</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Total Sources</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr"/>
-      <c r="D122" s="7">
-        <f>D109+D110</f>
+          <t>Balance Check</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="n"/>
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="10">
+        <f>IF(ABS(D115-D121)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>Balance Check</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr"/>
-      <c r="C123" s="6" t="inlineStr"/>
+      <c r="A123" s="5" t="n"/>
+      <c r="B123" s="6" t="n"/>
+      <c r="C123" s="6" t="n"/>
       <c r="D123" s="10">
-        <f>IF(ABS(D105-D111)&lt;0.01,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124"/>
+        <f>N100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>EXIT CALCULATIONS</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="n"/>
+      <c r="C124" s="4" t="n"/>
+      <c r="D124" s="4">
+        <f>D121-D122+D123</f>
+        <v/>
+      </c>
+      <c r="E124" s="4" t="n"/>
+      <c r="F124" s="4" t="n"/>
+      <c r="G124" s="4" t="n"/>
+      <c r="H124" s="4" t="n"/>
+      <c r="I124" s="4" t="n"/>
+      <c r="J124" s="4" t="n"/>
+      <c r="K124" s="4" t="n"/>
+      <c r="L124" s="4" t="n"/>
+      <c r="M124" s="4" t="n"/>
+      <c r="N124" s="4" t="n"/>
+    </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>EXIT CALCULATIONS</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="n"/>
-      <c r="C125" s="4" t="n"/>
-      <c r="D125" s="4" t="n"/>
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Cumulative Depreciation</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>Dep × Operating Years</t>
+        </is>
+      </c>
+      <c r="D125" s="4">
+        <f>$D$65*(10-3+1)</f>
+        <v/>
+      </c>
       <c r="E125" s="4" t="n"/>
       <c r="F125" s="4" t="n"/>
       <c r="G125" s="4" t="n"/>
@@ -5495,12 +6023,15 @@
       <c r="K125" s="4" t="n"/>
       <c r="L125" s="4" t="n"/>
       <c r="M125" s="4" t="n"/>
-      <c r="N125" s="4" t="n"/>
+      <c r="N125" s="15">
+        <f>$D$55*8</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Cumulative Depreciation</t>
+          <t>Exit RAB</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
@@ -5510,18 +6041,22 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Dep × Operating Years</t>
-        </is>
+          <t>RAB at COD - Cum Dep</t>
+        </is>
+      </c>
+      <c r="D126">
+        <f>$D$63-D125</f>
+        <v/>
       </c>
       <c r="N126" s="15">
-        <f>$D$55*8</f>
+        <f>$D$53-N115</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Exit RAB</t>
+          <t>Exit EV</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
@@ -5531,18 +6066,58 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>RAB at COD - Cum Dep</t>
-        </is>
+          <t>Exit RAB × xRAB Multiple</t>
+        </is>
+      </c>
+      <c r="D127">
+        <f>D126*$D$54</f>
+        <v/>
+      </c>
+      <c r="E127">
+        <f>-E69</f>
+        <v/>
+      </c>
+      <c r="F127">
+        <f>-F70</f>
+        <v/>
+      </c>
+      <c r="G127">
+        <f>-G71+G105</f>
+        <v/>
+      </c>
+      <c r="H127">
+        <f>H105</f>
+        <v/>
+      </c>
+      <c r="I127">
+        <f>I105</f>
+        <v/>
+      </c>
+      <c r="J127">
+        <f>J105</f>
+        <v/>
+      </c>
+      <c r="K127">
+        <f>K105</f>
+        <v/>
+      </c>
+      <c r="L127">
+        <f>L105</f>
+        <v/>
+      </c>
+      <c r="M127">
+        <f>M105</f>
+        <v/>
       </c>
       <c r="N127" s="15">
-        <f>$D$53-N115</f>
+        <f>N105+D124</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Exit EV</t>
+          <t>Exit Debt Payoff</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
@@ -5552,15 +6127,22 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Exit RAB × xRAB Multiple</t>
-        </is>
-      </c>
-      <c r="N128" s="15" t="inlineStr"/>
+          <t>Ending Bal at Exit</t>
+        </is>
+      </c>
+      <c r="D128" s="55">
+        <f>N94</f>
+        <v/>
+      </c>
+      <c r="N128" s="15">
+        <f>N84</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Exit Debt Payoff</t>
+          <t>DSRA Release</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
@@ -5570,18 +6152,22 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Ending Bal at Exit</t>
-        </is>
+          <t>DSRA Ending at Exit</t>
+        </is>
+      </c>
+      <c r="D129" s="56">
+        <f>N101</f>
+        <v/>
       </c>
       <c r="N129" s="15">
-        <f>N84</f>
+        <f>N91</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>DSRA Release</t>
+          <t>Exit Equity Proceeds</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
@@ -5591,190 +6177,274 @@
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>DSRA Ending at Exit</t>
-        </is>
-      </c>
-      <c r="N130" s="15">
-        <f>N91</f>
+          <t>Exit EV - Debt + DSRA</t>
+        </is>
+      </c>
+      <c r="D130">
+        <f>D127-D128+D129</f>
+        <v/>
+      </c>
+      <c r="N130" s="7">
+        <f>N117-N118+N119</f>
         <v/>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>Exit Equity Proceeds</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>Exit EV - Debt + DSRA</t>
-        </is>
-      </c>
-      <c r="N131" s="7" t="inlineStr"/>
-    </row>
-    <row r="132"/>
+      <c r="A131" s="5" t="n"/>
+      <c r="B131" s="6" t="n"/>
+      <c r="C131" s="6" t="n"/>
+      <c r="N131" s="7" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>EQUITY RETURNS</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="n"/>
+      <c r="C132" s="4" t="n"/>
+      <c r="D132" s="4" t="n"/>
+      <c r="E132" s="4" t="n"/>
+      <c r="F132" s="4" t="n"/>
+      <c r="G132" s="4" t="n"/>
+      <c r="H132" s="4" t="n"/>
+      <c r="I132" s="4" t="n"/>
+      <c r="J132" s="4" t="n"/>
+      <c r="K132" s="4" t="n"/>
+      <c r="L132" s="4" t="n"/>
+      <c r="M132" s="4" t="n"/>
+      <c r="N132" s="4" t="n"/>
+    </row>
     <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>EQUITY RETURNS</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="n"/>
-      <c r="C133" s="4" t="n"/>
-      <c r="D133" s="4" t="n"/>
-      <c r="E133" s="4" t="n"/>
-      <c r="F133" s="4" t="n"/>
-      <c r="G133" s="4" t="n"/>
-      <c r="H133" s="4" t="n"/>
-      <c r="I133" s="4" t="n"/>
-      <c r="J133" s="4" t="n"/>
-      <c r="K133" s="4" t="n"/>
-      <c r="L133" s="4" t="n"/>
-      <c r="M133" s="4" t="n"/>
-      <c r="N133" s="4" t="n"/>
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Equity Cash Flow</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="n"/>
+      <c r="D133" s="15">
+        <f>-D68</f>
+        <v/>
+      </c>
+      <c r="E133" s="15">
+        <f>-E69</f>
+        <v/>
+      </c>
+      <c r="F133" s="15">
+        <f>-F70</f>
+        <v/>
+      </c>
+      <c r="G133" s="15">
+        <f>-G71+G106</f>
+        <v/>
+      </c>
+      <c r="H133" s="15">
+        <f>H106</f>
+        <v/>
+      </c>
+      <c r="I133" s="15">
+        <f>I106</f>
+        <v/>
+      </c>
+      <c r="J133" s="15">
+        <f>J106</f>
+        <v/>
+      </c>
+      <c r="K133" s="15">
+        <f>K106</f>
+        <v/>
+      </c>
+      <c r="L133" s="15">
+        <f>L106</f>
+        <v/>
+      </c>
+      <c r="M133" s="15">
+        <f>M106</f>
+        <v/>
+      </c>
+      <c r="N133" s="15">
+        <f>N106+D130</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Equity Cash Flow</t>
+          <t>Levered IRR</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr"/>
-      <c r="D134" s="15" t="inlineStr"/>
-      <c r="E134" s="15" t="inlineStr"/>
-      <c r="F134" s="15" t="inlineStr"/>
-      <c r="G134" s="15" t="inlineStr"/>
-      <c r="H134" s="15" t="inlineStr"/>
-      <c r="I134" s="15" t="inlineStr"/>
-      <c r="J134" s="15" t="inlineStr"/>
-      <c r="K134" s="15" t="inlineStr"/>
-      <c r="L134" s="15" t="inlineStr"/>
-      <c r="M134" s="15" t="inlineStr"/>
-      <c r="N134" s="15" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
+      </c>
+      <c r="D134" s="26" t="n"/>
+      <c r="E134" s="15" t="n"/>
+      <c r="F134" s="15" t="n"/>
+      <c r="G134" s="15" t="n"/>
+      <c r="H134" s="15" t="n"/>
+      <c r="I134" s="15" t="n"/>
+      <c r="J134" s="15" t="n"/>
+      <c r="K134" s="15" t="n"/>
+      <c r="L134" s="15" t="n"/>
+      <c r="M134" s="15" t="n"/>
+      <c r="N134" s="15" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
+          <t>MOIC</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr"/>
-      <c r="D135" s="26" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Sum inflows / outflows</t>
+        </is>
+      </c>
+      <c r="D135" s="25" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>Sum inflows / outflows</t>
-        </is>
-      </c>
-      <c r="D136" s="25" t="inlineStr"/>
-    </row>
-    <row r="137"/>
+      <c r="A136" s="5" t="n"/>
+      <c r="B136" s="6" t="n"/>
+      <c r="C136" s="6" t="n"/>
+      <c r="D136" s="25" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="18" t="inlineStr">
+        <is>
+          <t>Unlevered Returns (for reference)</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="n"/>
+      <c r="C137" s="6" t="n"/>
+    </row>
     <row r="138">
-      <c r="A138" s="18" t="inlineStr">
-        <is>
-          <t>Unlevered Returns (for reference)</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr"/>
-      <c r="C138" s="6" t="inlineStr"/>
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>Unlevered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="n"/>
+      <c r="D138" s="15">
+        <f>-$D$63</f>
+        <v/>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" s="15">
+        <f>G86</f>
+        <v/>
+      </c>
+      <c r="H138" s="15">
+        <f>H86</f>
+        <v/>
+      </c>
+      <c r="I138" s="15">
+        <f>I86</f>
+        <v/>
+      </c>
+      <c r="J138" s="15">
+        <f>J86</f>
+        <v/>
+      </c>
+      <c r="K138" s="15">
+        <f>K86</f>
+        <v/>
+      </c>
+      <c r="L138" s="15">
+        <f>L86</f>
+        <v/>
+      </c>
+      <c r="M138" s="15">
+        <f>M86</f>
+        <v/>
+      </c>
+      <c r="N138" s="15">
+        <f>N86+D127</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Unlevered Cash Flow</t>
+          <t>Unlevered IRR</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr"/>
-      <c r="D139" s="15">
-        <f>-$D$17</f>
-        <v/>
-      </c>
-      <c r="E139" s="15">
-        <f>-$D$18</f>
-        <v/>
-      </c>
-      <c r="F139" s="15">
-        <f>-$D$19</f>
-        <v/>
-      </c>
-      <c r="G139" s="15">
-        <f>G76</f>
-        <v/>
-      </c>
-      <c r="H139" s="15">
-        <f>H76</f>
-        <v/>
-      </c>
-      <c r="I139" s="15">
-        <f>I76</f>
-        <v/>
-      </c>
-      <c r="J139" s="15">
-        <f>J76</f>
-        <v/>
-      </c>
-      <c r="K139" s="15">
-        <f>K76</f>
-        <v/>
-      </c>
-      <c r="L139" s="15">
-        <f>L76</f>
-        <v/>
-      </c>
-      <c r="M139" s="15">
-        <f>M76</f>
-        <v/>
-      </c>
-      <c r="N139" s="15">
-        <f>N76+N117</f>
-        <v/>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
+      </c>
+      <c r="D139" s="26">
+        <f>IRR(D138:N138)</f>
+        <v/>
+      </c>
+      <c r="E139" s="15" t="n"/>
+      <c r="F139" s="15" t="n"/>
+      <c r="G139" s="15" t="n"/>
+      <c r="H139" s="15" t="n"/>
+      <c r="I139" s="15" t="n"/>
+      <c r="J139" s="15" t="n"/>
+      <c r="K139" s="15" t="n"/>
+      <c r="L139" s="15" t="n"/>
+      <c r="M139" s="15" t="n"/>
+      <c r="N139" s="15" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr"/>
-      <c r="D140" s="26" t="inlineStr"/>
-    </row>
+      <c r="A140" s="5" t="n"/>
+      <c r="B140" s="6" t="n"/>
+      <c r="C140" s="6" t="n"/>
+      <c r="D140" s="26" t="n"/>
+    </row>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
@@ -3075,7 +3075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3474,7 +3474,7 @@
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="10">
-        <f>IF(N84&lt;1,"PASS","FAIL")</f>
+        <f>IF(N94&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -3501,7 +3501,6 @@
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="10" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -6425,26 +6424,6 @@
       <c r="C140" s="6" t="n"/>
       <c r="D140" s="26" t="n"/>
     </row>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
@@ -3450,10 +3450,7 @@
       </c>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
-      <c r="D21" s="10">
-        <f>D112</f>
-        <v/>
-      </c>
+      <c r="D21" s="10" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
@@ -3491,7 +3488,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>IF(D6&gt;=1.35,"PASS","FAIL")</f>
+        <f>IF(MINIFS(G95:N95,G95:N95,"&gt;0")&gt;=1.35,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_4_Transmission.xlsx
@@ -3249,10 +3249,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="n"/>
-      <c r="B6" s="44" t="n"/>
-      <c r="C6" s="44" t="n"/>
-      <c r="D6" s="44" t="n"/>
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="B6" s="44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>Minimum debt service coverage ratio</t>
+        </is>
+      </c>
+      <c r="D6" s="56">
+        <f>IF(COUNTIF(G95:N95,"&gt;0")&gt;0,MINIFS(G95:N95,G95:N95,"&gt;0"),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="45" t="inlineStr">
@@ -3488,7 +3503,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>IF(MINIFS(G95:N95,G95:N95,"&gt;0")&gt;=1.35,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.35,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
